--- a/12. 19 Januari 2026/JADWAL DAN KALDIK.xlsx
+++ b/12. 19 Januari 2026/JADWAL DAN KALDIK.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04375C5E-C285-46BE-AFC2-7CDBB2CF5E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7154942-5E8B-4149-BB2A-7AC6CC58DD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11040" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="282">
   <si>
     <t>KALENDER PENDIDIKAN MADRASAH BAITUL IZZAH 2025/2026</t>
   </si>
@@ -878,6 +878,9 @@
   </si>
   <si>
     <t>Di kantor, Ingatkan japri</t>
+  </si>
+  <si>
+    <t>6 : Rapat Kesantrian</t>
   </si>
 </sst>
 </file>
@@ -3222,6 +3225,150 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="27" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="74" fillId="11" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3240,6 +3387,90 @@
     <xf numFmtId="0" fontId="74" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="17" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="44" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="17" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="41" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="41" borderId="50" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="41" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="41" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="41" borderId="50" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="41" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="17" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="17" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="17" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="50" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="50" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="50" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="22" borderId="17" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3315,236 +3546,8 @@
     <xf numFmtId="0" fontId="1" fillId="40" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="17" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="44" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="17" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="41" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="41" borderId="50" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="41" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="41" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="41" borderId="50" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="41" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="17" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="17" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="17" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="50" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="49" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="50" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="46" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="50" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="64" fillId="37" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="27" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3842,16 +3845,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:17" ht="30">
-      <c r="D1" s="352" t="s">
+      <c r="D1" s="400" t="s">
         <v>226</v>
       </c>
-      <c r="E1" s="352"/>
-      <c r="F1" s="352"/>
-      <c r="G1" s="352"/>
-      <c r="H1" s="352"/>
-      <c r="I1" s="352"/>
-      <c r="J1" s="352"/>
-      <c r="K1" s="352"/>
+      <c r="E1" s="400"/>
+      <c r="F1" s="400"/>
+      <c r="G1" s="400"/>
+      <c r="H1" s="400"/>
+      <c r="I1" s="400"/>
+      <c r="J1" s="400"/>
+      <c r="K1" s="400"/>
     </row>
     <row r="3" spans="4:17" s="336" customFormat="1" ht="36.75" customHeight="1" thickBot="1">
       <c r="D3" s="335" t="s">
@@ -3878,14 +3881,14 @@
       <c r="K3" s="335" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="351" t="s">
+      <c r="O3" s="399" t="s">
         <v>229</v>
       </c>
-      <c r="P3" s="351"/>
-      <c r="Q3" s="351"/>
+      <c r="P3" s="399"/>
+      <c r="Q3" s="399"/>
     </row>
     <row r="4" spans="4:17" ht="24.95" customHeight="1" thickTop="1">
-      <c r="D4" s="353">
+      <c r="D4" s="401">
         <v>1</v>
       </c>
       <c r="E4" s="338" t="s">
@@ -3915,23 +3918,23 @@
       <c r="P4" s="340"/>
     </row>
     <row r="5" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D5" s="354"/>
+      <c r="D5" s="402"/>
       <c r="E5" s="341" t="s">
         <v>233</v>
       </c>
-      <c r="F5" s="350" t="s">
+      <c r="F5" s="398" t="s">
         <v>234</v>
       </c>
-      <c r="G5" s="350"/>
-      <c r="H5" s="350"/>
-      <c r="I5" s="350"/>
-      <c r="J5" s="350"/>
-      <c r="K5" s="350"/>
+      <c r="G5" s="398"/>
+      <c r="H5" s="398"/>
+      <c r="I5" s="398"/>
+      <c r="J5" s="398"/>
+      <c r="K5" s="398"/>
       <c r="O5" s="340"/>
       <c r="P5" s="340"/>
     </row>
     <row r="6" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D6" s="354"/>
+      <c r="D6" s="402"/>
       <c r="E6" s="342" t="s">
         <v>235</v>
       </c>
@@ -3957,7 +3960,7 @@
       <c r="P6" s="340"/>
     </row>
     <row r="7" spans="4:17" ht="24.95" hidden="1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="D7" s="354"/>
+      <c r="D7" s="402"/>
       <c r="E7" s="342"/>
       <c r="F7" s="343"/>
       <c r="G7" s="343"/>
@@ -3971,23 +3974,23 @@
       <c r="P7" s="340"/>
     </row>
     <row r="8" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D8" s="354"/>
+      <c r="D8" s="402"/>
       <c r="E8" s="341" t="s">
         <v>243</v>
       </c>
-      <c r="F8" s="350" t="s">
+      <c r="F8" s="398" t="s">
         <v>244</v>
       </c>
-      <c r="G8" s="350"/>
-      <c r="H8" s="350"/>
-      <c r="I8" s="350"/>
-      <c r="J8" s="350"/>
-      <c r="K8" s="350"/>
+      <c r="G8" s="398"/>
+      <c r="H8" s="398"/>
+      <c r="I8" s="398"/>
+      <c r="J8" s="398"/>
+      <c r="K8" s="398"/>
       <c r="O8" s="340"/>
       <c r="P8" s="340"/>
     </row>
     <row r="9" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D9" s="349">
+      <c r="D9" s="397">
         <v>2</v>
       </c>
       <c r="E9" s="344" t="s">
@@ -4017,23 +4020,23 @@
       <c r="P9" s="340"/>
     </row>
     <row r="10" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D10" s="349"/>
+      <c r="D10" s="397"/>
       <c r="E10" s="341" t="s">
         <v>233</v>
       </c>
-      <c r="F10" s="350" t="s">
+      <c r="F10" s="398" t="s">
         <v>234</v>
       </c>
-      <c r="G10" s="350"/>
-      <c r="H10" s="350"/>
-      <c r="I10" s="350"/>
-      <c r="J10" s="350"/>
-      <c r="K10" s="350"/>
+      <c r="G10" s="398"/>
+      <c r="H10" s="398"/>
+      <c r="I10" s="398"/>
+      <c r="J10" s="398"/>
+      <c r="K10" s="398"/>
       <c r="O10" s="340"/>
       <c r="P10" s="340"/>
     </row>
     <row r="11" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D11" s="349"/>
+      <c r="D11" s="397"/>
       <c r="E11" s="344" t="s">
         <v>235</v>
       </c>
@@ -4055,31 +4058,31 @@
       <c r="K11" s="345" t="s">
         <v>240</v>
       </c>
-      <c r="O11" s="351" t="s">
+      <c r="O11" s="399" t="s">
         <v>246</v>
       </c>
-      <c r="P11" s="351"/>
-      <c r="Q11" s="351"/>
+      <c r="P11" s="399"/>
+      <c r="Q11" s="399"/>
     </row>
     <row r="12" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D12" s="349"/>
+      <c r="D12" s="397"/>
       <c r="E12" s="341" t="s">
         <v>243</v>
       </c>
-      <c r="F12" s="350" t="s">
+      <c r="F12" s="398" t="s">
         <v>244</v>
       </c>
-      <c r="G12" s="350"/>
-      <c r="H12" s="350"/>
-      <c r="I12" s="350"/>
-      <c r="J12" s="350"/>
-      <c r="K12" s="350"/>
+      <c r="G12" s="398"/>
+      <c r="H12" s="398"/>
+      <c r="I12" s="398"/>
+      <c r="J12" s="398"/>
+      <c r="K12" s="398"/>
       <c r="O12" s="337"/>
       <c r="P12" s="337"/>
       <c r="Q12" s="337"/>
     </row>
     <row r="13" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D13" s="349">
+      <c r="D13" s="397">
         <v>3</v>
       </c>
       <c r="E13" s="344" t="s">
@@ -4109,23 +4112,23 @@
       <c r="P13" s="346"/>
     </row>
     <row r="14" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D14" s="349"/>
+      <c r="D14" s="397"/>
       <c r="E14" s="341" t="s">
         <v>233</v>
       </c>
-      <c r="F14" s="350" t="s">
+      <c r="F14" s="398" t="s">
         <v>234</v>
       </c>
-      <c r="G14" s="350"/>
-      <c r="H14" s="350"/>
-      <c r="I14" s="350"/>
-      <c r="J14" s="350"/>
-      <c r="K14" s="350"/>
+      <c r="G14" s="398"/>
+      <c r="H14" s="398"/>
+      <c r="I14" s="398"/>
+      <c r="J14" s="398"/>
+      <c r="K14" s="398"/>
       <c r="O14" s="346"/>
       <c r="P14" s="346"/>
     </row>
     <row r="15" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D15" s="349"/>
+      <c r="D15" s="397"/>
       <c r="E15" s="344" t="s">
         <v>235</v>
       </c>
@@ -4153,7 +4156,7 @@
       <c r="P15" s="346"/>
     </row>
     <row r="16" spans="4:17" ht="24.95" hidden="1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="D16" s="349"/>
+      <c r="D16" s="397"/>
       <c r="E16" s="344" t="s">
         <v>249</v>
       </c>
@@ -4165,14 +4168,14 @@
       <c r="I16" s="345"/>
       <c r="J16" s="345"/>
       <c r="K16" s="345"/>
-      <c r="O16" s="351" t="s">
+      <c r="O16" s="399" t="s">
         <v>251</v>
       </c>
-      <c r="P16" s="351"/>
-      <c r="Q16" s="351"/>
+      <c r="P16" s="399"/>
+      <c r="Q16" s="399"/>
     </row>
     <row r="17" spans="4:17" ht="24.95" hidden="1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="D17" s="349"/>
+      <c r="D17" s="397"/>
       <c r="E17" s="344" t="s">
         <v>249</v>
       </c>
@@ -4191,7 +4194,7 @@
       <c r="Q17" s="346"/>
     </row>
     <row r="18" spans="4:17" ht="24.95" hidden="1" customHeight="1" thickTop="1" thickBot="1">
-      <c r="D18" s="349"/>
+      <c r="D18" s="397"/>
       <c r="E18" s="344" t="s">
         <v>249</v>
       </c>
@@ -4210,18 +4213,18 @@
       <c r="Q18" s="347"/>
     </row>
     <row r="19" spans="4:17" ht="24.95" customHeight="1">
-      <c r="D19" s="349"/>
+      <c r="D19" s="397"/>
       <c r="E19" s="341" t="s">
         <v>243</v>
       </c>
-      <c r="F19" s="350" t="s">
+      <c r="F19" s="398" t="s">
         <v>244</v>
       </c>
-      <c r="G19" s="350"/>
-      <c r="H19" s="350"/>
-      <c r="I19" s="350"/>
-      <c r="J19" s="350"/>
-      <c r="K19" s="350"/>
+      <c r="G19" s="398"/>
+      <c r="H19" s="398"/>
+      <c r="I19" s="398"/>
+      <c r="J19" s="398"/>
+      <c r="K19" s="398"/>
       <c r="O19" s="347"/>
       <c r="P19" s="347"/>
       <c r="Q19" s="347"/>
@@ -4325,20 +4328,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="356" t="s">
+      <c r="A1" s="432" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="356"/>
-      <c r="C1" s="356"/>
-      <c r="D1" s="356"/>
+      <c r="B1" s="432"/>
+      <c r="C1" s="432"/>
+      <c r="D1" s="432"/>
     </row>
     <row r="2" spans="1:5" ht="21">
-      <c r="A2" s="356" t="s">
+      <c r="A2" s="432" t="s">
         <v>160</v>
       </c>
-      <c r="B2" s="356"/>
-      <c r="C2" s="356"/>
-      <c r="D2" s="356"/>
+      <c r="B2" s="432"/>
+      <c r="C2" s="432"/>
+      <c r="D2" s="432"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="312"/>
@@ -4361,10 +4364,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
-      <c r="A5" s="357">
+      <c r="A5" s="433">
         <v>1</v>
       </c>
-      <c r="B5" s="360" t="s">
+      <c r="B5" s="436" t="s">
         <v>165</v>
       </c>
       <c r="C5" s="314" t="s">
@@ -4375,8 +4378,8 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
-      <c r="A6" s="358"/>
-      <c r="B6" s="361"/>
+      <c r="A6" s="434"/>
+      <c r="B6" s="437"/>
       <c r="C6" s="315" t="s">
         <v>168</v>
       </c>
@@ -4385,24 +4388,24 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="358"/>
-      <c r="B7" s="361"/>
-      <c r="C7" s="363" t="s">
+      <c r="A7" s="434"/>
+      <c r="B7" s="437"/>
+      <c r="C7" s="439" t="s">
         <v>170</v>
       </c>
-      <c r="D7" s="363" t="s">
+      <c r="D7" s="439" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="0.75" customHeight="1">
-      <c r="A8" s="358"/>
-      <c r="B8" s="361"/>
-      <c r="C8" s="364"/>
-      <c r="D8" s="364"/>
+      <c r="A8" s="434"/>
+      <c r="B8" s="437"/>
+      <c r="C8" s="440"/>
+      <c r="D8" s="440"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="358"/>
-      <c r="B9" s="361"/>
+      <c r="A9" s="434"/>
+      <c r="B9" s="437"/>
       <c r="C9" s="314" t="s">
         <v>172</v>
       </c>
@@ -4411,8 +4414,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
-      <c r="A10" s="358"/>
-      <c r="B10" s="361"/>
+      <c r="A10" s="434"/>
+      <c r="B10" s="437"/>
       <c r="C10" s="314" t="s">
         <v>174</v>
       </c>
@@ -4422,8 +4425,8 @@
       <c r="E10" s="316"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
-      <c r="A11" s="358"/>
-      <c r="B11" s="361"/>
+      <c r="A11" s="434"/>
+      <c r="B11" s="437"/>
       <c r="C11" s="314" t="s">
         <v>176</v>
       </c>
@@ -4432,24 +4435,24 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
-      <c r="A12" s="358"/>
-      <c r="B12" s="361"/>
+      <c r="A12" s="434"/>
+      <c r="B12" s="437"/>
       <c r="C12" s="314"/>
       <c r="D12" s="314" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
-      <c r="A13" s="358"/>
-      <c r="B13" s="361"/>
+      <c r="A13" s="434"/>
+      <c r="B13" s="437"/>
       <c r="C13" s="317"/>
       <c r="D13" s="314" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
-      <c r="A14" s="359"/>
-      <c r="B14" s="362"/>
+      <c r="A14" s="435"/>
+      <c r="B14" s="438"/>
       <c r="C14" s="314" t="s">
         <v>180</v>
       </c>
@@ -4461,10 +4464,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
-      <c r="A15" s="365">
+      <c r="A15" s="441">
         <v>2</v>
       </c>
-      <c r="B15" s="368" t="s">
+      <c r="B15" s="444" t="s">
         <v>182</v>
       </c>
       <c r="C15" s="318" t="s">
@@ -4475,9 +4478,9 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1">
-      <c r="A16" s="366"/>
-      <c r="B16" s="369"/>
-      <c r="C16" s="371" t="s">
+      <c r="A16" s="442"/>
+      <c r="B16" s="445"/>
+      <c r="C16" s="447" t="s">
         <v>184</v>
       </c>
       <c r="D16" s="318" t="s">
@@ -4485,74 +4488,74 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1">
-      <c r="A17" s="366"/>
-      <c r="B17" s="369"/>
-      <c r="C17" s="372"/>
+      <c r="A17" s="442"/>
+      <c r="B17" s="445"/>
+      <c r="C17" s="448"/>
       <c r="D17" s="318" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1">
-      <c r="A18" s="366"/>
-      <c r="B18" s="369"/>
-      <c r="C18" s="372"/>
+      <c r="A18" s="442"/>
+      <c r="B18" s="445"/>
+      <c r="C18" s="448"/>
       <c r="D18" s="318" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1">
-      <c r="A19" s="366"/>
-      <c r="B19" s="369"/>
-      <c r="C19" s="372"/>
+      <c r="A19" s="442"/>
+      <c r="B19" s="445"/>
+      <c r="C19" s="448"/>
       <c r="D19" s="318" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1">
-      <c r="A20" s="366"/>
-      <c r="B20" s="369"/>
-      <c r="C20" s="372"/>
+      <c r="A20" s="442"/>
+      <c r="B20" s="445"/>
+      <c r="C20" s="448"/>
       <c r="D20" s="318" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1">
-      <c r="A21" s="366"/>
-      <c r="B21" s="369"/>
-      <c r="C21" s="372"/>
+      <c r="A21" s="442"/>
+      <c r="B21" s="445"/>
+      <c r="C21" s="448"/>
       <c r="D21" s="318" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1">
-      <c r="A22" s="366"/>
-      <c r="B22" s="369"/>
-      <c r="C22" s="372"/>
+      <c r="A22" s="442"/>
+      <c r="B22" s="445"/>
+      <c r="C22" s="448"/>
       <c r="D22" s="318" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1">
-      <c r="A23" s="366"/>
-      <c r="B23" s="369"/>
-      <c r="C23" s="372"/>
+      <c r="A23" s="442"/>
+      <c r="B23" s="445"/>
+      <c r="C23" s="448"/>
       <c r="D23" s="318" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1">
-      <c r="A24" s="367"/>
-      <c r="B24" s="370"/>
-      <c r="C24" s="373"/>
+      <c r="A24" s="443"/>
+      <c r="B24" s="446"/>
+      <c r="C24" s="449"/>
       <c r="D24" s="318" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" hidden="1" customHeight="1">
-      <c r="A25" s="374">
+      <c r="A25" s="450">
         <v>3</v>
       </c>
-      <c r="B25" s="377" t="s">
+      <c r="B25" s="453" t="s">
         <v>193</v>
       </c>
       <c r="C25" s="319" t="s">
@@ -4563,8 +4566,8 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" hidden="1" customHeight="1">
-      <c r="A26" s="375"/>
-      <c r="B26" s="378"/>
+      <c r="A26" s="451"/>
+      <c r="B26" s="454"/>
       <c r="C26" s="319" t="s">
         <v>195</v>
       </c>
@@ -4573,8 +4576,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" hidden="1" customHeight="1">
-      <c r="A27" s="375"/>
-      <c r="B27" s="378"/>
+      <c r="A27" s="451"/>
+      <c r="B27" s="454"/>
       <c r="C27" s="319" t="s">
         <v>184</v>
       </c>
@@ -4583,34 +4586,34 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="15" hidden="1" customHeight="1">
-      <c r="A28" s="375"/>
-      <c r="B28" s="378"/>
+      <c r="A28" s="451"/>
+      <c r="B28" s="454"/>
       <c r="C28" s="319"/>
       <c r="D28" s="319" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" hidden="1" customHeight="1">
-      <c r="A29" s="375"/>
-      <c r="B29" s="378"/>
+      <c r="A29" s="451"/>
+      <c r="B29" s="454"/>
       <c r="C29" s="319"/>
       <c r="D29" s="319" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" hidden="1" customHeight="1">
-      <c r="A30" s="376"/>
-      <c r="B30" s="379"/>
+      <c r="A30" s="452"/>
+      <c r="B30" s="455"/>
       <c r="C30" s="319"/>
       <c r="D30" s="319" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1">
-      <c r="A31" s="401">
+      <c r="A31" s="424">
         <v>4</v>
       </c>
-      <c r="B31" s="404" t="s">
+      <c r="B31" s="427" t="s">
         <v>199</v>
       </c>
       <c r="C31" s="320" t="s">
@@ -4621,8 +4624,8 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="402"/>
-      <c r="B32" s="405"/>
+      <c r="A32" s="425"/>
+      <c r="B32" s="428"/>
       <c r="C32" s="320" t="s">
         <v>201</v>
       </c>
@@ -4631,8 +4634,8 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="402"/>
-      <c r="B33" s="405"/>
+      <c r="A33" s="425"/>
+      <c r="B33" s="428"/>
       <c r="C33" s="320" t="s">
         <v>172</v>
       </c>
@@ -4641,8 +4644,8 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="402"/>
-      <c r="B34" s="405"/>
+      <c r="A34" s="425"/>
+      <c r="B34" s="428"/>
       <c r="C34" s="321" t="s">
         <v>202</v>
       </c>
@@ -4651,9 +4654,9 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="402"/>
-      <c r="B35" s="405"/>
-      <c r="C35" s="386" t="s">
+      <c r="A35" s="425"/>
+      <c r="B35" s="428"/>
+      <c r="C35" s="409" t="s">
         <v>184</v>
       </c>
       <c r="D35" s="320" t="s">
@@ -4661,70 +4664,70 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="402"/>
-      <c r="B36" s="405"/>
-      <c r="C36" s="407"/>
+      <c r="A36" s="425"/>
+      <c r="B36" s="428"/>
+      <c r="C36" s="430"/>
       <c r="D36" s="320" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="402"/>
-      <c r="B37" s="405"/>
-      <c r="C37" s="407"/>
+      <c r="A37" s="425"/>
+      <c r="B37" s="428"/>
+      <c r="C37" s="430"/>
       <c r="D37" s="320" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A38" s="402"/>
-      <c r="B38" s="405"/>
-      <c r="C38" s="407"/>
+      <c r="A38" s="425"/>
+      <c r="B38" s="428"/>
+      <c r="C38" s="430"/>
       <c r="D38" s="320" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A39" s="402"/>
-      <c r="B39" s="405"/>
-      <c r="C39" s="407"/>
+      <c r="A39" s="425"/>
+      <c r="B39" s="428"/>
+      <c r="C39" s="430"/>
       <c r="D39" s="320" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="0.75" customHeight="1">
-      <c r="A40" s="402"/>
-      <c r="B40" s="405"/>
-      <c r="C40" s="387"/>
+      <c r="A40" s="425"/>
+      <c r="B40" s="428"/>
+      <c r="C40" s="410"/>
       <c r="D40" s="320"/>
     </row>
     <row r="41" spans="1:4" hidden="1">
-      <c r="A41" s="402"/>
-      <c r="B41" s="405"/>
-      <c r="C41" s="355"/>
-      <c r="D41" s="386"/>
+      <c r="A41" s="425"/>
+      <c r="B41" s="428"/>
+      <c r="C41" s="431"/>
+      <c r="D41" s="409"/>
     </row>
     <row r="42" spans="1:4" ht="3" hidden="1" customHeight="1">
-      <c r="A42" s="402"/>
-      <c r="B42" s="405"/>
-      <c r="C42" s="355"/>
-      <c r="D42" s="387"/>
+      <c r="A42" s="425"/>
+      <c r="B42" s="428"/>
+      <c r="C42" s="431"/>
+      <c r="D42" s="410"/>
     </row>
     <row r="43" spans="1:4" hidden="1">
-      <c r="A43" s="402"/>
-      <c r="B43" s="405"/>
-      <c r="C43" s="355"/>
+      <c r="A43" s="425"/>
+      <c r="B43" s="428"/>
+      <c r="C43" s="431"/>
       <c r="D43" s="320"/>
     </row>
     <row r="44" spans="1:4" hidden="1">
-      <c r="A44" s="402"/>
-      <c r="B44" s="405"/>
-      <c r="C44" s="355"/>
+      <c r="A44" s="425"/>
+      <c r="B44" s="428"/>
+      <c r="C44" s="431"/>
       <c r="D44" s="320"/>
     </row>
     <row r="45" spans="1:4" hidden="1">
-      <c r="A45" s="402"/>
-      <c r="B45" s="405"/>
+      <c r="A45" s="425"/>
+      <c r="B45" s="428"/>
       <c r="C45" s="322" t="s">
         <v>204</v>
       </c>
@@ -4733,8 +4736,8 @@
       </c>
     </row>
     <row r="46" spans="1:4" hidden="1">
-      <c r="A46" s="403"/>
-      <c r="B46" s="406"/>
+      <c r="A46" s="426"/>
+      <c r="B46" s="429"/>
       <c r="C46" s="322" t="s">
         <v>206</v>
       </c>
@@ -4752,7 +4755,7 @@
       <c r="C47" s="325" t="s">
         <v>166</v>
       </c>
-      <c r="D47" s="388" t="s">
+      <c r="D47" s="411" t="s">
         <v>209</v>
       </c>
     </row>
@@ -4766,13 +4769,13 @@
       <c r="C48" s="325" t="s">
         <v>166</v>
       </c>
-      <c r="D48" s="389"/>
+      <c r="D48" s="412"/>
     </row>
     <row r="49" spans="1:4" s="326" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A49" s="390">
+      <c r="A49" s="413">
         <v>5</v>
       </c>
-      <c r="B49" s="393" t="s">
+      <c r="B49" s="416" t="s">
         <v>211</v>
       </c>
       <c r="C49" s="327" t="s">
@@ -4783,8 +4786,8 @@
       </c>
     </row>
     <row r="50" spans="1:4" s="326" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A50" s="391"/>
-      <c r="B50" s="394"/>
+      <c r="A50" s="414"/>
+      <c r="B50" s="417"/>
       <c r="C50" s="327" t="s">
         <v>201</v>
       </c>
@@ -4793,8 +4796,8 @@
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="391"/>
-      <c r="B51" s="394"/>
+      <c r="A51" s="414"/>
+      <c r="B51" s="417"/>
       <c r="C51" s="329" t="s">
         <v>172</v>
       </c>
@@ -4803,9 +4806,9 @@
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="391"/>
-      <c r="B52" s="394"/>
-      <c r="C52" s="393" t="s">
+      <c r="A52" s="414"/>
+      <c r="B52" s="417"/>
+      <c r="C52" s="416" t="s">
         <v>184</v>
       </c>
       <c r="D52" s="327" t="s">
@@ -4813,42 +4816,42 @@
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="391"/>
-      <c r="B53" s="394"/>
-      <c r="C53" s="394"/>
+      <c r="A53" s="414"/>
+      <c r="B53" s="417"/>
+      <c r="C53" s="417"/>
       <c r="D53" s="327" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="391"/>
-      <c r="B54" s="394"/>
-      <c r="C54" s="394"/>
+      <c r="A54" s="414"/>
+      <c r="B54" s="417"/>
+      <c r="C54" s="417"/>
       <c r="D54" s="327" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="391"/>
-      <c r="B55" s="394"/>
-      <c r="C55" s="394"/>
+      <c r="A55" s="414"/>
+      <c r="B55" s="417"/>
+      <c r="C55" s="417"/>
       <c r="D55" s="327" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="392"/>
-      <c r="B56" s="395"/>
-      <c r="C56" s="395"/>
+      <c r="A56" s="415"/>
+      <c r="B56" s="418"/>
+      <c r="C56" s="418"/>
       <c r="D56" s="327" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="396">
+      <c r="A57" s="419">
         <v>6</v>
       </c>
-      <c r="B57" s="397" t="s">
+      <c r="B57" s="420" t="s">
         <v>217</v>
       </c>
       <c r="C57" s="330" t="s">
@@ -4859,9 +4862,9 @@
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="396"/>
-      <c r="B58" s="397"/>
-      <c r="C58" s="398" t="s">
+      <c r="A58" s="419"/>
+      <c r="B58" s="420"/>
+      <c r="C58" s="421" t="s">
         <v>201</v>
       </c>
       <c r="D58" s="331" t="s">
@@ -4869,14 +4872,14 @@
       </c>
     </row>
     <row r="59" spans="1:4" hidden="1">
-      <c r="A59" s="396"/>
-      <c r="B59" s="397"/>
-      <c r="C59" s="399"/>
+      <c r="A59" s="419"/>
+      <c r="B59" s="420"/>
+      <c r="C59" s="422"/>
       <c r="D59" s="331"/>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="396"/>
-      <c r="B60" s="397"/>
+      <c r="A60" s="419"/>
+      <c r="B60" s="420"/>
       <c r="C60" s="330" t="s">
         <v>172</v>
       </c>
@@ -4885,9 +4888,9 @@
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="396"/>
-      <c r="B61" s="397"/>
-      <c r="C61" s="400" t="s">
+      <c r="A61" s="419"/>
+      <c r="B61" s="420"/>
+      <c r="C61" s="423" t="s">
         <v>184</v>
       </c>
       <c r="D61" s="331" t="s">
@@ -4895,76 +4898,76 @@
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="396"/>
-      <c r="B62" s="397"/>
-      <c r="C62" s="400"/>
+      <c r="A62" s="419"/>
+      <c r="B62" s="420"/>
+      <c r="C62" s="423"/>
       <c r="D62" s="331" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="396"/>
-      <c r="B63" s="397"/>
-      <c r="C63" s="400"/>
+      <c r="A63" s="419"/>
+      <c r="B63" s="420"/>
+      <c r="C63" s="423"/>
       <c r="D63" s="331" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="396"/>
-      <c r="B64" s="397"/>
-      <c r="C64" s="400"/>
+      <c r="A64" s="419"/>
+      <c r="B64" s="420"/>
+      <c r="C64" s="423"/>
       <c r="D64" s="331" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="396"/>
-      <c r="B65" s="397"/>
-      <c r="C65" s="400"/>
+      <c r="A65" s="419"/>
+      <c r="B65" s="420"/>
+      <c r="C65" s="423"/>
       <c r="D65" s="331" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="396"/>
-      <c r="B66" s="397"/>
-      <c r="C66" s="400"/>
+      <c r="A66" s="419"/>
+      <c r="B66" s="420"/>
+      <c r="C66" s="423"/>
       <c r="D66" s="331" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="396"/>
-      <c r="B67" s="397"/>
-      <c r="C67" s="400"/>
+      <c r="A67" s="419"/>
+      <c r="B67" s="420"/>
+      <c r="C67" s="423"/>
       <c r="D67" s="331" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="68" spans="1:4" hidden="1">
-      <c r="A68" s="396"/>
-      <c r="B68" s="397"/>
-      <c r="C68" s="400"/>
+      <c r="A68" s="419"/>
+      <c r="B68" s="420"/>
+      <c r="C68" s="423"/>
       <c r="D68" s="331"/>
     </row>
     <row r="69" spans="1:4" hidden="1">
-      <c r="A69" s="396"/>
-      <c r="B69" s="397"/>
-      <c r="C69" s="400"/>
+      <c r="A69" s="419"/>
+      <c r="B69" s="420"/>
+      <c r="C69" s="423"/>
       <c r="D69" s="331"/>
     </row>
     <row r="70" spans="1:4" hidden="1">
-      <c r="A70" s="396"/>
-      <c r="B70" s="397"/>
-      <c r="C70" s="400"/>
+      <c r="A70" s="419"/>
+      <c r="B70" s="420"/>
+      <c r="C70" s="423"/>
       <c r="D70" s="331"/>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="380">
+      <c r="A71" s="403">
         <v>7</v>
       </c>
-      <c r="B71" s="381" t="s">
+      <c r="B71" s="404" t="s">
         <v>223</v>
       </c>
       <c r="C71" s="332" t="s">
@@ -4975,9 +4978,9 @@
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="380"/>
-      <c r="B72" s="382"/>
-      <c r="C72" s="383" t="s">
+      <c r="A72" s="403"/>
+      <c r="B72" s="405"/>
+      <c r="C72" s="406" t="s">
         <v>201</v>
       </c>
       <c r="D72" s="319" t="s">
@@ -4985,14 +4988,14 @@
       </c>
     </row>
     <row r="73" spans="1:4" ht="0.75" customHeight="1">
-      <c r="A73" s="380"/>
-      <c r="B73" s="382"/>
-      <c r="C73" s="384"/>
+      <c r="A73" s="403"/>
+      <c r="B73" s="405"/>
+      <c r="C73" s="407"/>
       <c r="D73" s="319"/>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="380"/>
-      <c r="B74" s="382"/>
+      <c r="A74" s="403"/>
+      <c r="B74" s="405"/>
       <c r="C74" s="332" t="s">
         <v>172</v>
       </c>
@@ -5001,8 +5004,8 @@
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="380"/>
-      <c r="B75" s="382"/>
+      <c r="A75" s="403"/>
+      <c r="B75" s="405"/>
       <c r="C75" s="332" t="s">
         <v>225</v>
       </c>
@@ -5011,9 +5014,9 @@
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="380"/>
-      <c r="B76" s="382"/>
-      <c r="C76" s="385" t="s">
+      <c r="A76" s="403"/>
+      <c r="B76" s="405"/>
+      <c r="C76" s="408" t="s">
         <v>184</v>
       </c>
       <c r="D76" s="319" t="s">
@@ -5021,71 +5024,71 @@
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="380"/>
-      <c r="B77" s="382"/>
-      <c r="C77" s="385"/>
+      <c r="A77" s="403"/>
+      <c r="B77" s="405"/>
+      <c r="C77" s="408"/>
       <c r="D77" s="319" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="380"/>
-      <c r="B78" s="382"/>
-      <c r="C78" s="385"/>
+      <c r="A78" s="403"/>
+      <c r="B78" s="405"/>
+      <c r="C78" s="408"/>
       <c r="D78" s="319" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="380"/>
-      <c r="B79" s="382"/>
-      <c r="C79" s="385"/>
+      <c r="A79" s="403"/>
+      <c r="B79" s="405"/>
+      <c r="C79" s="408"/>
       <c r="D79" s="319" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="380"/>
-      <c r="B80" s="382"/>
-      <c r="C80" s="385"/>
+      <c r="A80" s="403"/>
+      <c r="B80" s="405"/>
+      <c r="C80" s="408"/>
       <c r="D80" s="319" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="380"/>
-      <c r="B81" s="382"/>
-      <c r="C81" s="385"/>
+      <c r="A81" s="403"/>
+      <c r="B81" s="405"/>
+      <c r="C81" s="408"/>
       <c r="D81" s="319" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="380"/>
-      <c r="B82" s="382"/>
-      <c r="C82" s="385"/>
+      <c r="A82" s="403"/>
+      <c r="B82" s="405"/>
+      <c r="C82" s="408"/>
       <c r="D82" s="319" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="380"/>
-      <c r="B83" s="382"/>
-      <c r="C83" s="385"/>
+      <c r="A83" s="403"/>
+      <c r="B83" s="405"/>
+      <c r="C83" s="408"/>
       <c r="D83" s="319" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="380"/>
-      <c r="B84" s="382"/>
-      <c r="C84" s="385"/>
+      <c r="A84" s="403"/>
+      <c r="B84" s="405"/>
+      <c r="C84" s="408"/>
       <c r="D84" s="319"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="380"/>
-      <c r="B85" s="382"/>
-      <c r="C85" s="385"/>
+      <c r="A85" s="403"/>
+      <c r="B85" s="405"/>
+      <c r="C85" s="408"/>
       <c r="D85" s="319"/>
     </row>
     <row r="86" spans="1:5">
@@ -5158,6 +5161,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A5:A14"/>
+    <mergeCell ref="B5:B14"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A15:A24"/>
+    <mergeCell ref="B15:B24"/>
+    <mergeCell ref="C16:C24"/>
+    <mergeCell ref="A25:A30"/>
+    <mergeCell ref="B25:B30"/>
     <mergeCell ref="A71:A85"/>
     <mergeCell ref="B71:B85"/>
     <mergeCell ref="C72:C73"/>
@@ -5174,18 +5189,6 @@
     <mergeCell ref="A31:A46"/>
     <mergeCell ref="B31:B46"/>
     <mergeCell ref="C35:C40"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A5:A14"/>
-    <mergeCell ref="B5:B14"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A15:A24"/>
-    <mergeCell ref="B15:B24"/>
-    <mergeCell ref="C16:C24"/>
-    <mergeCell ref="A25:A30"/>
-    <mergeCell ref="B25:B30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5210,19 +5213,19 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:12" ht="31.5">
-      <c r="B3" s="408" t="s">
+      <c r="B3" s="456" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="408"/>
-      <c r="D3" s="408"/>
-      <c r="E3" s="408"/>
-      <c r="F3" s="408"/>
-      <c r="G3" s="408"/>
-      <c r="H3" s="408"/>
-      <c r="I3" s="408"/>
-      <c r="J3" s="408"/>
-      <c r="K3" s="408"/>
-      <c r="L3" s="408"/>
+      <c r="C3" s="456"/>
+      <c r="D3" s="456"/>
+      <c r="E3" s="456"/>
+      <c r="F3" s="456"/>
+      <c r="G3" s="456"/>
+      <c r="H3" s="456"/>
+      <c r="I3" s="456"/>
+      <c r="J3" s="456"/>
+      <c r="K3" s="456"/>
+      <c r="L3" s="456"/>
     </row>
     <row r="5" spans="2:12" ht="21">
       <c r="B5" s="285" t="s">
@@ -5940,365 +5943,365 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:89 16342:16384" ht="34.5" customHeight="1">
-      <c r="A1" s="415" t="s">
+      <c r="A1" s="395" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="415"/>
-      <c r="C1" s="415"/>
-      <c r="D1" s="415"/>
-      <c r="E1" s="415"/>
-      <c r="F1" s="415"/>
-      <c r="G1" s="415"/>
-      <c r="H1" s="415"/>
-      <c r="I1" s="415"/>
-      <c r="J1" s="415"/>
-      <c r="K1" s="415"/>
-      <c r="L1" s="415"/>
-      <c r="M1" s="415"/>
-      <c r="N1" s="415"/>
-      <c r="O1" s="415"/>
-      <c r="P1" s="415"/>
-      <c r="Q1" s="415"/>
-      <c r="R1" s="415"/>
-      <c r="S1" s="415"/>
-      <c r="T1" s="415"/>
-      <c r="U1" s="415"/>
-      <c r="V1" s="415"/>
-      <c r="W1" s="415"/>
-      <c r="X1" s="415"/>
-      <c r="Y1" s="415"/>
-      <c r="Z1" s="415"/>
-      <c r="AA1" s="415"/>
-      <c r="AB1" s="415"/>
-      <c r="AC1" s="415"/>
-      <c r="AD1" s="415"/>
-      <c r="AE1" s="415"/>
-      <c r="AF1" s="415"/>
-      <c r="AG1" s="415"/>
-      <c r="AH1" s="415"/>
-      <c r="AI1" s="415"/>
-      <c r="AJ1" s="415"/>
-      <c r="AK1" s="415"/>
-      <c r="AL1" s="415"/>
-      <c r="AM1" s="415"/>
-      <c r="AN1" s="415"/>
-      <c r="AO1" s="415"/>
-      <c r="AP1" s="415"/>
-      <c r="AQ1" s="415"/>
-      <c r="AR1" s="415"/>
-      <c r="AS1" s="415"/>
-      <c r="AT1" s="415"/>
-      <c r="AU1" s="415"/>
-      <c r="AV1" s="415"/>
-      <c r="AW1" s="415"/>
-      <c r="AX1" s="415"/>
-      <c r="AY1" s="415"/>
-      <c r="AZ1" s="415"/>
-      <c r="BA1" s="415"/>
-      <c r="BB1" s="415"/>
-      <c r="BC1" s="415"/>
-      <c r="BD1" s="415"/>
-      <c r="BE1" s="415"/>
-      <c r="BF1" s="415"/>
-      <c r="BG1" s="415"/>
-      <c r="BH1" s="415"/>
-      <c r="BI1" s="415"/>
-      <c r="BJ1" s="415"/>
-      <c r="BK1" s="415"/>
-      <c r="BL1" s="415"/>
-      <c r="BM1" s="415"/>
-      <c r="BN1" s="415"/>
-      <c r="BO1" s="415"/>
-      <c r="BP1" s="415"/>
-      <c r="BQ1" s="415"/>
-      <c r="BR1" s="415"/>
-      <c r="BS1" s="415"/>
-      <c r="BT1" s="415"/>
-      <c r="BU1" s="415"/>
-      <c r="BV1" s="415"/>
-      <c r="BW1" s="415"/>
-      <c r="BX1" s="415"/>
-      <c r="BY1" s="415"/>
-      <c r="BZ1" s="415"/>
-      <c r="CA1" s="415"/>
-      <c r="CB1" s="415"/>
-      <c r="CC1" s="415"/>
-      <c r="CD1" s="415"/>
-      <c r="CE1" s="415"/>
-      <c r="CF1" s="415"/>
-      <c r="CG1" s="415"/>
-      <c r="CH1" s="415"/>
-      <c r="CI1" s="415"/>
-      <c r="CJ1" s="415"/>
-      <c r="CK1" s="415"/>
+      <c r="B1" s="395"/>
+      <c r="C1" s="395"/>
+      <c r="D1" s="395"/>
+      <c r="E1" s="395"/>
+      <c r="F1" s="395"/>
+      <c r="G1" s="395"/>
+      <c r="H1" s="395"/>
+      <c r="I1" s="395"/>
+      <c r="J1" s="395"/>
+      <c r="K1" s="395"/>
+      <c r="L1" s="395"/>
+      <c r="M1" s="395"/>
+      <c r="N1" s="395"/>
+      <c r="O1" s="395"/>
+      <c r="P1" s="395"/>
+      <c r="Q1" s="395"/>
+      <c r="R1" s="395"/>
+      <c r="S1" s="395"/>
+      <c r="T1" s="395"/>
+      <c r="U1" s="395"/>
+      <c r="V1" s="395"/>
+      <c r="W1" s="395"/>
+      <c r="X1" s="395"/>
+      <c r="Y1" s="395"/>
+      <c r="Z1" s="395"/>
+      <c r="AA1" s="395"/>
+      <c r="AB1" s="395"/>
+      <c r="AC1" s="395"/>
+      <c r="AD1" s="395"/>
+      <c r="AE1" s="395"/>
+      <c r="AF1" s="395"/>
+      <c r="AG1" s="395"/>
+      <c r="AH1" s="395"/>
+      <c r="AI1" s="395"/>
+      <c r="AJ1" s="395"/>
+      <c r="AK1" s="395"/>
+      <c r="AL1" s="395"/>
+      <c r="AM1" s="395"/>
+      <c r="AN1" s="395"/>
+      <c r="AO1" s="395"/>
+      <c r="AP1" s="395"/>
+      <c r="AQ1" s="395"/>
+      <c r="AR1" s="395"/>
+      <c r="AS1" s="395"/>
+      <c r="AT1" s="395"/>
+      <c r="AU1" s="395"/>
+      <c r="AV1" s="395"/>
+      <c r="AW1" s="395"/>
+      <c r="AX1" s="395"/>
+      <c r="AY1" s="395"/>
+      <c r="AZ1" s="395"/>
+      <c r="BA1" s="395"/>
+      <c r="BB1" s="395"/>
+      <c r="BC1" s="395"/>
+      <c r="BD1" s="395"/>
+      <c r="BE1" s="395"/>
+      <c r="BF1" s="395"/>
+      <c r="BG1" s="395"/>
+      <c r="BH1" s="395"/>
+      <c r="BI1" s="395"/>
+      <c r="BJ1" s="395"/>
+      <c r="BK1" s="395"/>
+      <c r="BL1" s="395"/>
+      <c r="BM1" s="395"/>
+      <c r="BN1" s="395"/>
+      <c r="BO1" s="395"/>
+      <c r="BP1" s="395"/>
+      <c r="BQ1" s="395"/>
+      <c r="BR1" s="395"/>
+      <c r="BS1" s="395"/>
+      <c r="BT1" s="395"/>
+      <c r="BU1" s="395"/>
+      <c r="BV1" s="395"/>
+      <c r="BW1" s="395"/>
+      <c r="BX1" s="395"/>
+      <c r="BY1" s="395"/>
+      <c r="BZ1" s="395"/>
+      <c r="CA1" s="395"/>
+      <c r="CB1" s="395"/>
+      <c r="CC1" s="395"/>
+      <c r="CD1" s="395"/>
+      <c r="CE1" s="395"/>
+      <c r="CF1" s="395"/>
+      <c r="CG1" s="395"/>
+      <c r="CH1" s="395"/>
+      <c r="CI1" s="395"/>
+      <c r="CJ1" s="395"/>
+      <c r="CK1" s="395"/>
     </row>
     <row r="3" spans="1:89 16342:16384" s="2" customFormat="1" ht="23.1" customHeight="1">
-      <c r="A3" s="416" t="s">
+      <c r="A3" s="376" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="417"/>
-      <c r="C3" s="417"/>
-      <c r="D3" s="417"/>
-      <c r="E3" s="417"/>
-      <c r="F3" s="417"/>
-      <c r="G3" s="417"/>
-      <c r="H3" s="417"/>
-      <c r="I3" s="417"/>
-      <c r="J3" s="417"/>
-      <c r="K3" s="417"/>
-      <c r="L3" s="417"/>
-      <c r="M3" s="417"/>
-      <c r="N3" s="417"/>
-      <c r="P3" s="418" t="s">
+      <c r="B3" s="377"/>
+      <c r="C3" s="377"/>
+      <c r="D3" s="377"/>
+      <c r="E3" s="377"/>
+      <c r="F3" s="377"/>
+      <c r="G3" s="377"/>
+      <c r="H3" s="377"/>
+      <c r="I3" s="377"/>
+      <c r="J3" s="377"/>
+      <c r="K3" s="377"/>
+      <c r="L3" s="377"/>
+      <c r="M3" s="377"/>
+      <c r="N3" s="377"/>
+      <c r="P3" s="380" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="419"/>
-      <c r="R3" s="419"/>
-      <c r="S3" s="419"/>
-      <c r="T3" s="419"/>
-      <c r="U3" s="419"/>
-      <c r="V3" s="419"/>
-      <c r="W3" s="419"/>
-      <c r="X3" s="419"/>
-      <c r="Y3" s="419"/>
-      <c r="Z3" s="419"/>
-      <c r="AA3" s="419"/>
-      <c r="AB3" s="419"/>
-      <c r="AC3" s="419"/>
-      <c r="AE3" s="418" t="s">
+      <c r="Q3" s="396"/>
+      <c r="R3" s="396"/>
+      <c r="S3" s="396"/>
+      <c r="T3" s="396"/>
+      <c r="U3" s="396"/>
+      <c r="V3" s="396"/>
+      <c r="W3" s="396"/>
+      <c r="X3" s="396"/>
+      <c r="Y3" s="396"/>
+      <c r="Z3" s="396"/>
+      <c r="AA3" s="396"/>
+      <c r="AB3" s="396"/>
+      <c r="AC3" s="396"/>
+      <c r="AE3" s="380" t="s">
         <v>3</v>
       </c>
-      <c r="AF3" s="420"/>
-      <c r="AG3" s="420"/>
-      <c r="AH3" s="420"/>
-      <c r="AI3" s="420"/>
-      <c r="AJ3" s="420"/>
-      <c r="AK3" s="420"/>
-      <c r="AL3" s="420"/>
-      <c r="AM3" s="420"/>
-      <c r="AN3" s="420"/>
-      <c r="AO3" s="420"/>
-      <c r="AP3" s="420"/>
-      <c r="AQ3" s="420"/>
-      <c r="AR3" s="420"/>
-      <c r="AT3" s="418" t="s">
+      <c r="AF3" s="381"/>
+      <c r="AG3" s="381"/>
+      <c r="AH3" s="381"/>
+      <c r="AI3" s="381"/>
+      <c r="AJ3" s="381"/>
+      <c r="AK3" s="381"/>
+      <c r="AL3" s="381"/>
+      <c r="AM3" s="381"/>
+      <c r="AN3" s="381"/>
+      <c r="AO3" s="381"/>
+      <c r="AP3" s="381"/>
+      <c r="AQ3" s="381"/>
+      <c r="AR3" s="381"/>
+      <c r="AT3" s="380" t="s">
         <v>4</v>
       </c>
-      <c r="AU3" s="420"/>
-      <c r="AV3" s="420"/>
-      <c r="AW3" s="420"/>
-      <c r="AX3" s="420"/>
-      <c r="AY3" s="420"/>
-      <c r="AZ3" s="420"/>
-      <c r="BA3" s="420"/>
-      <c r="BB3" s="420"/>
-      <c r="BC3" s="420"/>
-      <c r="BD3" s="420"/>
-      <c r="BE3" s="420"/>
-      <c r="BF3" s="420"/>
-      <c r="BG3" s="420"/>
-      <c r="BI3" s="418" t="s">
+      <c r="AU3" s="381"/>
+      <c r="AV3" s="381"/>
+      <c r="AW3" s="381"/>
+      <c r="AX3" s="381"/>
+      <c r="AY3" s="381"/>
+      <c r="AZ3" s="381"/>
+      <c r="BA3" s="381"/>
+      <c r="BB3" s="381"/>
+      <c r="BC3" s="381"/>
+      <c r="BD3" s="381"/>
+      <c r="BE3" s="381"/>
+      <c r="BF3" s="381"/>
+      <c r="BG3" s="381"/>
+      <c r="BI3" s="380" t="s">
         <v>5</v>
       </c>
-      <c r="BJ3" s="420"/>
-      <c r="BK3" s="420"/>
-      <c r="BL3" s="420"/>
-      <c r="BM3" s="420"/>
-      <c r="BN3" s="420"/>
-      <c r="BO3" s="420"/>
-      <c r="BP3" s="420"/>
-      <c r="BQ3" s="420"/>
-      <c r="BR3" s="420"/>
-      <c r="BS3" s="420"/>
-      <c r="BT3" s="420"/>
-      <c r="BU3" s="420"/>
-      <c r="BV3" s="420"/>
-      <c r="BX3" s="418" t="s">
+      <c r="BJ3" s="381"/>
+      <c r="BK3" s="381"/>
+      <c r="BL3" s="381"/>
+      <c r="BM3" s="381"/>
+      <c r="BN3" s="381"/>
+      <c r="BO3" s="381"/>
+      <c r="BP3" s="381"/>
+      <c r="BQ3" s="381"/>
+      <c r="BR3" s="381"/>
+      <c r="BS3" s="381"/>
+      <c r="BT3" s="381"/>
+      <c r="BU3" s="381"/>
+      <c r="BV3" s="381"/>
+      <c r="BX3" s="380" t="s">
         <v>6</v>
       </c>
-      <c r="BY3" s="420"/>
-      <c r="BZ3" s="420"/>
-      <c r="CA3" s="420"/>
-      <c r="CB3" s="420"/>
-      <c r="CC3" s="420"/>
-      <c r="CD3" s="420"/>
-      <c r="CE3" s="420"/>
-      <c r="CF3" s="420"/>
-      <c r="CG3" s="420"/>
-      <c r="CH3" s="420"/>
-      <c r="CI3" s="420"/>
-      <c r="CJ3" s="420"/>
-      <c r="CK3" s="420"/>
+      <c r="BY3" s="381"/>
+      <c r="BZ3" s="381"/>
+      <c r="CA3" s="381"/>
+      <c r="CB3" s="381"/>
+      <c r="CC3" s="381"/>
+      <c r="CD3" s="381"/>
+      <c r="CE3" s="381"/>
+      <c r="CF3" s="381"/>
+      <c r="CG3" s="381"/>
+      <c r="CH3" s="381"/>
+      <c r="CI3" s="381"/>
+      <c r="CJ3" s="381"/>
+      <c r="CK3" s="381"/>
     </row>
     <row r="4" spans="1:89 16342:16384" s="3" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="409" t="s">
+      <c r="A4" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="410"/>
-      <c r="C4" s="409" t="s">
+      <c r="B4" s="375"/>
+      <c r="C4" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="411"/>
-      <c r="E4" s="409" t="s">
+      <c r="D4" s="371"/>
+      <c r="E4" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="412"/>
-      <c r="G4" s="409" t="s">
+      <c r="F4" s="372"/>
+      <c r="G4" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="411"/>
-      <c r="I4" s="409" t="s">
+      <c r="H4" s="371"/>
+      <c r="I4" s="370" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="411"/>
-      <c r="K4" s="413" t="s">
+      <c r="J4" s="371"/>
+      <c r="K4" s="373" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="414"/>
-      <c r="M4" s="409" t="s">
+      <c r="L4" s="374"/>
+      <c r="M4" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="410"/>
-      <c r="P4" s="409" t="s">
+      <c r="N4" s="375"/>
+      <c r="P4" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" s="410"/>
-      <c r="R4" s="409" t="s">
+      <c r="Q4" s="375"/>
+      <c r="R4" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="S4" s="411"/>
-      <c r="T4" s="409" t="s">
+      <c r="S4" s="371"/>
+      <c r="T4" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="412"/>
-      <c r="V4" s="409" t="s">
+      <c r="U4" s="372"/>
+      <c r="V4" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="W4" s="411"/>
-      <c r="X4" s="409" t="s">
+      <c r="W4" s="371"/>
+      <c r="X4" s="370" t="s">
         <v>11</v>
       </c>
-      <c r="Y4" s="411"/>
-      <c r="Z4" s="413" t="s">
+      <c r="Y4" s="371"/>
+      <c r="Z4" s="373" t="s">
         <v>12</v>
       </c>
-      <c r="AA4" s="414"/>
-      <c r="AB4" s="409" t="s">
+      <c r="AA4" s="374"/>
+      <c r="AB4" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="410"/>
-      <c r="AE4" s="409" t="s">
+      <c r="AC4" s="375"/>
+      <c r="AE4" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="AF4" s="410"/>
-      <c r="AG4" s="409" t="s">
+      <c r="AF4" s="375"/>
+      <c r="AG4" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="AH4" s="411"/>
-      <c r="AI4" s="409" t="s">
+      <c r="AH4" s="371"/>
+      <c r="AI4" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="AJ4" s="412"/>
-      <c r="AK4" s="409" t="s">
+      <c r="AJ4" s="372"/>
+      <c r="AK4" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="AL4" s="411"/>
-      <c r="AM4" s="409" t="s">
+      <c r="AL4" s="371"/>
+      <c r="AM4" s="370" t="s">
         <v>11</v>
       </c>
-      <c r="AN4" s="411"/>
-      <c r="AO4" s="413" t="s">
+      <c r="AN4" s="371"/>
+      <c r="AO4" s="373" t="s">
         <v>12</v>
       </c>
-      <c r="AP4" s="414"/>
-      <c r="AQ4" s="409" t="s">
+      <c r="AP4" s="374"/>
+      <c r="AQ4" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="AR4" s="410"/>
-      <c r="AT4" s="409" t="s">
+      <c r="AR4" s="375"/>
+      <c r="AT4" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="AU4" s="410"/>
-      <c r="AV4" s="409" t="s">
+      <c r="AU4" s="375"/>
+      <c r="AV4" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="AW4" s="411"/>
-      <c r="AX4" s="409" t="s">
+      <c r="AW4" s="371"/>
+      <c r="AX4" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="AY4" s="412"/>
-      <c r="AZ4" s="409" t="s">
+      <c r="AY4" s="372"/>
+      <c r="AZ4" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="BA4" s="411"/>
-      <c r="BB4" s="409" t="s">
+      <c r="BA4" s="371"/>
+      <c r="BB4" s="370" t="s">
         <v>11</v>
       </c>
-      <c r="BC4" s="411"/>
-      <c r="BD4" s="413" t="s">
+      <c r="BC4" s="371"/>
+      <c r="BD4" s="373" t="s">
         <v>12</v>
       </c>
-      <c r="BE4" s="414"/>
-      <c r="BF4" s="409" t="s">
+      <c r="BE4" s="374"/>
+      <c r="BF4" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="BG4" s="410"/>
-      <c r="BI4" s="409" t="s">
+      <c r="BG4" s="375"/>
+      <c r="BI4" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="BJ4" s="410"/>
-      <c r="BK4" s="409" t="s">
+      <c r="BJ4" s="375"/>
+      <c r="BK4" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="BL4" s="411"/>
-      <c r="BM4" s="409" t="s">
+      <c r="BL4" s="371"/>
+      <c r="BM4" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="BN4" s="412"/>
-      <c r="BO4" s="409" t="s">
+      <c r="BN4" s="372"/>
+      <c r="BO4" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="BP4" s="411"/>
-      <c r="BQ4" s="409" t="s">
+      <c r="BP4" s="371"/>
+      <c r="BQ4" s="370" t="s">
         <v>11</v>
       </c>
-      <c r="BR4" s="411"/>
-      <c r="BS4" s="413" t="s">
+      <c r="BR4" s="371"/>
+      <c r="BS4" s="373" t="s">
         <v>12</v>
       </c>
-      <c r="BT4" s="414"/>
-      <c r="BU4" s="409" t="s">
+      <c r="BT4" s="374"/>
+      <c r="BU4" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="BV4" s="410"/>
-      <c r="BX4" s="409" t="s">
+      <c r="BV4" s="375"/>
+      <c r="BX4" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="BY4" s="410"/>
-      <c r="BZ4" s="409" t="s">
+      <c r="BY4" s="375"/>
+      <c r="BZ4" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="CA4" s="411"/>
-      <c r="CB4" s="409" t="s">
+      <c r="CA4" s="371"/>
+      <c r="CB4" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="CC4" s="412"/>
-      <c r="CD4" s="409" t="s">
+      <c r="CC4" s="372"/>
+      <c r="CD4" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="CE4" s="411"/>
-      <c r="CF4" s="409" t="s">
+      <c r="CE4" s="371"/>
+      <c r="CF4" s="370" t="s">
         <v>11</v>
       </c>
-      <c r="CG4" s="411"/>
-      <c r="CH4" s="413" t="s">
+      <c r="CG4" s="371"/>
+      <c r="CH4" s="373" t="s">
         <v>12</v>
       </c>
-      <c r="CI4" s="414"/>
-      <c r="CJ4" s="409" t="s">
+      <c r="CI4" s="374"/>
+      <c r="CJ4" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="CK4" s="410"/>
+      <c r="CK4" s="375"/>
       <c r="XDN4" s="4"/>
       <c r="XDO4" s="4"/>
       <c r="XDP4" s="4"/>
@@ -6344,8 +6347,8 @@
       <c r="XFD4" s="4"/>
     </row>
     <row r="5" spans="1:89 16342:16384" s="2" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A5" s="428"/>
-      <c r="B5" s="429"/>
+      <c r="A5" s="393"/>
+      <c r="B5" s="394"/>
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
       <c r="E5" s="7">
@@ -6416,18 +6419,18 @@
       <c r="AC5" s="20">
         <v>13</v>
       </c>
-      <c r="AE5" s="430"/>
-      <c r="AF5" s="422"/>
-      <c r="AG5" s="430"/>
-      <c r="AH5" s="431"/>
-      <c r="AI5" s="430"/>
-      <c r="AJ5" s="422"/>
-      <c r="AK5" s="430"/>
-      <c r="AL5" s="422"/>
-      <c r="AM5" s="421"/>
-      <c r="AN5" s="422"/>
-      <c r="AO5" s="421"/>
-      <c r="AP5" s="422"/>
+      <c r="AE5" s="361"/>
+      <c r="AF5" s="390"/>
+      <c r="AG5" s="361"/>
+      <c r="AH5" s="362"/>
+      <c r="AI5" s="361"/>
+      <c r="AJ5" s="390"/>
+      <c r="AK5" s="361"/>
+      <c r="AL5" s="390"/>
+      <c r="AM5" s="359"/>
+      <c r="AN5" s="390"/>
+      <c r="AO5" s="359"/>
+      <c r="AP5" s="390"/>
       <c r="AQ5" s="21">
         <v>1</v>
       </c>
@@ -6435,14 +6438,14 @@
         <v>10</v>
       </c>
       <c r="AS5" s="23"/>
-      <c r="AT5" s="423"/>
-      <c r="AU5" s="424"/>
-      <c r="AV5" s="423"/>
-      <c r="AW5" s="424"/>
-      <c r="AX5" s="423"/>
-      <c r="AY5" s="424"/>
-      <c r="AZ5" s="423"/>
-      <c r="BA5" s="424"/>
+      <c r="AT5" s="387"/>
+      <c r="AU5" s="388"/>
+      <c r="AV5" s="387"/>
+      <c r="AW5" s="388"/>
+      <c r="AX5" s="387"/>
+      <c r="AY5" s="388"/>
+      <c r="AZ5" s="387"/>
+      <c r="BA5" s="388"/>
       <c r="BB5" s="24">
         <v>1</v>
       </c>
@@ -7322,10 +7325,10 @@
       <c r="J9" s="40">
         <v>6</v>
       </c>
-      <c r="K9" s="421"/>
-      <c r="L9" s="425"/>
-      <c r="M9" s="426"/>
-      <c r="N9" s="427"/>
+      <c r="K9" s="359"/>
+      <c r="L9" s="360"/>
+      <c r="M9" s="391"/>
+      <c r="N9" s="392"/>
       <c r="P9" s="98">
         <v>28</v>
       </c>
@@ -7507,73 +7510,73 @@
       </c>
     </row>
     <row r="10" spans="1:89 16342:16384" s="2" customFormat="1" ht="26.1" customHeight="1">
-      <c r="A10" s="437" t="s">
+      <c r="A10" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="437"/>
-      <c r="C10" s="437"/>
-      <c r="D10" s="437"/>
-      <c r="E10" s="437"/>
-      <c r="F10" s="437"/>
-      <c r="G10" s="437"/>
-      <c r="H10" s="437"/>
-      <c r="I10" s="437"/>
-      <c r="J10" s="437"/>
-      <c r="K10" s="437"/>
-      <c r="L10" s="437"/>
-      <c r="M10" s="437"/>
-      <c r="N10" s="437"/>
-      <c r="P10" s="437" t="s">
+      <c r="B10" s="356"/>
+      <c r="C10" s="356"/>
+      <c r="D10" s="356"/>
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="G10" s="356"/>
+      <c r="H10" s="356"/>
+      <c r="I10" s="356"/>
+      <c r="J10" s="356"/>
+      <c r="K10" s="356"/>
+      <c r="L10" s="356"/>
+      <c r="M10" s="356"/>
+      <c r="N10" s="356"/>
+      <c r="P10" s="356" t="s">
         <v>15</v>
       </c>
-      <c r="Q10" s="437"/>
-      <c r="R10" s="437"/>
-      <c r="S10" s="437"/>
-      <c r="T10" s="437"/>
-      <c r="U10" s="437"/>
-      <c r="V10" s="437"/>
-      <c r="W10" s="437"/>
-      <c r="X10" s="437"/>
-      <c r="Y10" s="437"/>
-      <c r="Z10" s="437"/>
-      <c r="AA10" s="437"/>
-      <c r="AB10" s="437"/>
-      <c r="AC10" s="437"/>
+      <c r="Q10" s="356"/>
+      <c r="R10" s="356"/>
+      <c r="S10" s="356"/>
+      <c r="T10" s="356"/>
+      <c r="U10" s="356"/>
+      <c r="V10" s="356"/>
+      <c r="W10" s="356"/>
+      <c r="X10" s="356"/>
+      <c r="Y10" s="356"/>
+      <c r="Z10" s="356"/>
+      <c r="AA10" s="356"/>
+      <c r="AB10" s="356"/>
+      <c r="AC10" s="356"/>
       <c r="AE10" s="43">
         <v>30</v>
       </c>
       <c r="AF10" s="54">
         <v>9</v>
       </c>
-      <c r="AG10" s="430"/>
-      <c r="AH10" s="422"/>
-      <c r="AI10" s="430"/>
-      <c r="AJ10" s="431"/>
-      <c r="AK10" s="430"/>
-      <c r="AL10" s="422"/>
-      <c r="AM10" s="430"/>
-      <c r="AN10" s="422"/>
-      <c r="AO10" s="430"/>
-      <c r="AP10" s="422"/>
-      <c r="AQ10" s="430"/>
-      <c r="AR10" s="422"/>
+      <c r="AG10" s="361"/>
+      <c r="AH10" s="390"/>
+      <c r="AI10" s="361"/>
+      <c r="AJ10" s="362"/>
+      <c r="AK10" s="361"/>
+      <c r="AL10" s="390"/>
+      <c r="AM10" s="361"/>
+      <c r="AN10" s="390"/>
+      <c r="AO10" s="361"/>
+      <c r="AP10" s="390"/>
+      <c r="AQ10" s="361"/>
+      <c r="AR10" s="390"/>
       <c r="AS10" s="23"/>
-      <c r="AT10" s="423"/>
-      <c r="AU10" s="424">
+      <c r="AT10" s="387"/>
+      <c r="AU10" s="388">
         <v>5</v>
       </c>
-      <c r="AV10" s="423"/>
-      <c r="AW10" s="424"/>
-      <c r="AX10" s="423"/>
-      <c r="AY10" s="424"/>
-      <c r="AZ10" s="423"/>
-      <c r="BA10" s="424"/>
-      <c r="BB10" s="423"/>
-      <c r="BC10" s="424"/>
-      <c r="BD10" s="423"/>
-      <c r="BE10" s="424"/>
-      <c r="BF10" s="423"/>
-      <c r="BG10" s="424"/>
+      <c r="AV10" s="387"/>
+      <c r="AW10" s="388"/>
+      <c r="AX10" s="387"/>
+      <c r="AY10" s="388"/>
+      <c r="AZ10" s="387"/>
+      <c r="BA10" s="388"/>
+      <c r="BB10" s="387"/>
+      <c r="BC10" s="388"/>
+      <c r="BD10" s="387"/>
+      <c r="BE10" s="388"/>
+      <c r="BF10" s="387"/>
+      <c r="BG10" s="388"/>
       <c r="BI10" s="30"/>
       <c r="BJ10" s="116"/>
       <c r="BK10" s="30"/>
@@ -7651,90 +7654,90 @@
       <c r="XFD10" s="1"/>
     </row>
     <row r="11" spans="1:89 16342:16384" s="2" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A11" s="432" t="s">
+      <c r="A11" s="389" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="432"/>
-      <c r="C11" s="432"/>
-      <c r="D11" s="432"/>
-      <c r="E11" s="432"/>
-      <c r="F11" s="432"/>
-      <c r="G11" s="432"/>
-      <c r="P11" s="433" t="s">
+      <c r="B11" s="389"/>
+      <c r="C11" s="389"/>
+      <c r="D11" s="389"/>
+      <c r="E11" s="389"/>
+      <c r="F11" s="389"/>
+      <c r="G11" s="389"/>
+      <c r="P11" s="354" t="s">
         <v>17</v>
       </c>
-      <c r="Q11" s="433"/>
-      <c r="R11" s="433"/>
-      <c r="S11" s="433"/>
-      <c r="T11" s="433"/>
-      <c r="U11" s="433"/>
-      <c r="V11" s="433"/>
-      <c r="W11" s="433"/>
-      <c r="AE11" s="434" t="s">
+      <c r="Q11" s="354"/>
+      <c r="R11" s="354"/>
+      <c r="S11" s="354"/>
+      <c r="T11" s="354"/>
+      <c r="U11" s="354"/>
+      <c r="V11" s="354"/>
+      <c r="W11" s="354"/>
+      <c r="AE11" s="382" t="s">
         <v>18</v>
       </c>
-      <c r="AF11" s="435"/>
-      <c r="AG11" s="435"/>
-      <c r="AH11" s="435"/>
-      <c r="AI11" s="435"/>
-      <c r="AJ11" s="435"/>
-      <c r="AK11" s="435"/>
-      <c r="AL11" s="435"/>
-      <c r="AM11" s="435"/>
-      <c r="AN11" s="435"/>
-      <c r="AO11" s="435"/>
-      <c r="AP11" s="435"/>
-      <c r="AQ11" s="435"/>
-      <c r="AR11" s="436"/>
+      <c r="AF11" s="383"/>
+      <c r="AG11" s="383"/>
+      <c r="AH11" s="383"/>
+      <c r="AI11" s="383"/>
+      <c r="AJ11" s="383"/>
+      <c r="AK11" s="383"/>
+      <c r="AL11" s="383"/>
+      <c r="AM11" s="383"/>
+      <c r="AN11" s="383"/>
+      <c r="AO11" s="383"/>
+      <c r="AP11" s="383"/>
+      <c r="AQ11" s="383"/>
+      <c r="AR11" s="384"/>
       <c r="AS11" s="23"/>
-      <c r="AT11" s="434" t="s">
+      <c r="AT11" s="382" t="s">
         <v>19</v>
       </c>
-      <c r="AU11" s="435"/>
-      <c r="AV11" s="435"/>
-      <c r="AW11" s="435"/>
-      <c r="AX11" s="435"/>
-      <c r="AY11" s="435"/>
-      <c r="AZ11" s="435"/>
-      <c r="BA11" s="435"/>
-      <c r="BB11" s="435"/>
-      <c r="BC11" s="435"/>
-      <c r="BD11" s="435"/>
-      <c r="BE11" s="435"/>
-      <c r="BF11" s="435"/>
-      <c r="BG11" s="436"/>
-      <c r="BI11" s="434" t="s">
+      <c r="AU11" s="383"/>
+      <c r="AV11" s="383"/>
+      <c r="AW11" s="383"/>
+      <c r="AX11" s="383"/>
+      <c r="AY11" s="383"/>
+      <c r="AZ11" s="383"/>
+      <c r="BA11" s="383"/>
+      <c r="BB11" s="383"/>
+      <c r="BC11" s="383"/>
+      <c r="BD11" s="383"/>
+      <c r="BE11" s="383"/>
+      <c r="BF11" s="383"/>
+      <c r="BG11" s="384"/>
+      <c r="BI11" s="382" t="s">
         <v>20</v>
       </c>
-      <c r="BJ11" s="435"/>
-      <c r="BK11" s="435"/>
-      <c r="BL11" s="435"/>
-      <c r="BM11" s="435"/>
-      <c r="BN11" s="435"/>
-      <c r="BO11" s="435"/>
-      <c r="BP11" s="435"/>
-      <c r="BQ11" s="435"/>
-      <c r="BR11" s="435"/>
-      <c r="BS11" s="435"/>
-      <c r="BT11" s="435"/>
-      <c r="BU11" s="435"/>
-      <c r="BV11" s="436"/>
-      <c r="BX11" s="434" t="s">
+      <c r="BJ11" s="383"/>
+      <c r="BK11" s="383"/>
+      <c r="BL11" s="383"/>
+      <c r="BM11" s="383"/>
+      <c r="BN11" s="383"/>
+      <c r="BO11" s="383"/>
+      <c r="BP11" s="383"/>
+      <c r="BQ11" s="383"/>
+      <c r="BR11" s="383"/>
+      <c r="BS11" s="383"/>
+      <c r="BT11" s="383"/>
+      <c r="BU11" s="383"/>
+      <c r="BV11" s="384"/>
+      <c r="BX11" s="382" t="s">
         <v>18</v>
       </c>
-      <c r="BY11" s="435"/>
-      <c r="BZ11" s="435"/>
-      <c r="CA11" s="435"/>
-      <c r="CB11" s="435"/>
-      <c r="CC11" s="435"/>
-      <c r="CD11" s="435"/>
-      <c r="CE11" s="435"/>
-      <c r="CF11" s="435"/>
-      <c r="CG11" s="435"/>
-      <c r="CH11" s="435"/>
-      <c r="CI11" s="435"/>
-      <c r="CJ11" s="435"/>
-      <c r="CK11" s="436"/>
+      <c r="BY11" s="383"/>
+      <c r="BZ11" s="383"/>
+      <c r="CA11" s="383"/>
+      <c r="CB11" s="383"/>
+      <c r="CC11" s="383"/>
+      <c r="CD11" s="383"/>
+      <c r="CE11" s="383"/>
+      <c r="CF11" s="383"/>
+      <c r="CG11" s="383"/>
+      <c r="CH11" s="383"/>
+      <c r="CI11" s="383"/>
+      <c r="CJ11" s="383"/>
+      <c r="CK11" s="384"/>
     </row>
     <row r="12" spans="1:89 16342:16384" s="2" customFormat="1" ht="15.95" customHeight="1">
       <c r="A12" s="127">
@@ -7772,49 +7775,49 @@
       <c r="AA12" s="134"/>
       <c r="AB12" s="134"/>
       <c r="AC12" s="134"/>
-      <c r="AE12" s="433" t="s">
+      <c r="AE12" s="354" t="s">
         <v>23</v>
       </c>
-      <c r="AF12" s="433"/>
-      <c r="AG12" s="433"/>
-      <c r="AH12" s="433"/>
-      <c r="AI12" s="433"/>
-      <c r="AJ12" s="433"/>
-      <c r="AK12" s="433"/>
-      <c r="AL12" s="433"/>
-      <c r="AM12" s="433"/>
-      <c r="AT12" s="433" t="s">
+      <c r="AF12" s="354"/>
+      <c r="AG12" s="354"/>
+      <c r="AH12" s="354"/>
+      <c r="AI12" s="354"/>
+      <c r="AJ12" s="354"/>
+      <c r="AK12" s="354"/>
+      <c r="AL12" s="354"/>
+      <c r="AM12" s="354"/>
+      <c r="AT12" s="354" t="s">
         <v>24</v>
       </c>
-      <c r="AU12" s="433"/>
-      <c r="AV12" s="433"/>
-      <c r="AW12" s="433"/>
-      <c r="AX12" s="433"/>
-      <c r="AY12" s="433"/>
-      <c r="AZ12" s="433"/>
-      <c r="BA12" s="439"/>
-      <c r="BB12" s="439"/>
-      <c r="BC12" s="439"/>
-      <c r="BD12" s="439"/>
-      <c r="BE12" s="439"/>
-      <c r="BF12" s="439"/>
-      <c r="BG12" s="439"/>
-      <c r="BI12" s="433" t="s">
+      <c r="AU12" s="354"/>
+      <c r="AV12" s="354"/>
+      <c r="AW12" s="354"/>
+      <c r="AX12" s="354"/>
+      <c r="AY12" s="354"/>
+      <c r="AZ12" s="354"/>
+      <c r="BA12" s="385"/>
+      <c r="BB12" s="385"/>
+      <c r="BC12" s="385"/>
+      <c r="BD12" s="385"/>
+      <c r="BE12" s="385"/>
+      <c r="BF12" s="385"/>
+      <c r="BG12" s="385"/>
+      <c r="BI12" s="354" t="s">
         <v>25</v>
       </c>
-      <c r="BJ12" s="433"/>
-      <c r="BK12" s="433"/>
-      <c r="BL12" s="433"/>
-      <c r="BM12" s="433"/>
-      <c r="BN12" s="433"/>
-      <c r="BX12" s="440" t="s">
+      <c r="BJ12" s="354"/>
+      <c r="BK12" s="354"/>
+      <c r="BL12" s="354"/>
+      <c r="BM12" s="354"/>
+      <c r="BN12" s="354"/>
+      <c r="BX12" s="386" t="s">
         <v>26</v>
       </c>
-      <c r="BY12" s="440"/>
-      <c r="BZ12" s="440"/>
-      <c r="CA12" s="440"/>
-      <c r="CB12" s="440"/>
-      <c r="CC12" s="440"/>
+      <c r="BY12" s="386"/>
+      <c r="BZ12" s="386"/>
+      <c r="CA12" s="386"/>
+      <c r="CB12" s="386"/>
+      <c r="CC12" s="386"/>
     </row>
     <row r="13" spans="1:89 16342:16384" s="2" customFormat="1" ht="15.95" customHeight="1">
       <c r="A13" s="136">
@@ -7961,6 +7964,9 @@
       </c>
       <c r="BY14" s="138" t="s">
         <v>34</v>
+      </c>
+      <c r="CE14" s="2" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:89 16342:16384" s="2" customFormat="1" ht="15.95" customHeight="1">
@@ -8201,102 +8207,102 @@
       <c r="XFD18" s="1"/>
     </row>
     <row r="19" spans="1:89 16342:16384" s="2" customFormat="1" ht="24" customHeight="1">
-      <c r="A19" s="416" t="s">
+      <c r="A19" s="376" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="417"/>
-      <c r="C19" s="417"/>
-      <c r="D19" s="417"/>
-      <c r="E19" s="417"/>
-      <c r="F19" s="417"/>
-      <c r="G19" s="417"/>
-      <c r="H19" s="417"/>
-      <c r="I19" s="417"/>
-      <c r="J19" s="417"/>
-      <c r="K19" s="417"/>
-      <c r="L19" s="417"/>
-      <c r="M19" s="417"/>
-      <c r="N19" s="417"/>
-      <c r="P19" s="438" t="s">
+      <c r="B19" s="377"/>
+      <c r="C19" s="377"/>
+      <c r="D19" s="377"/>
+      <c r="E19" s="377"/>
+      <c r="F19" s="377"/>
+      <c r="G19" s="377"/>
+      <c r="H19" s="377"/>
+      <c r="I19" s="377"/>
+      <c r="J19" s="377"/>
+      <c r="K19" s="377"/>
+      <c r="L19" s="377"/>
+      <c r="M19" s="377"/>
+      <c r="N19" s="377"/>
+      <c r="P19" s="378" t="s">
         <v>56</v>
       </c>
-      <c r="Q19" s="441"/>
-      <c r="R19" s="441"/>
-      <c r="S19" s="441"/>
-      <c r="T19" s="441"/>
-      <c r="U19" s="441"/>
-      <c r="V19" s="441"/>
-      <c r="W19" s="441"/>
-      <c r="X19" s="441"/>
-      <c r="Y19" s="441"/>
-      <c r="Z19" s="441"/>
-      <c r="AA19" s="441"/>
-      <c r="AB19" s="441"/>
-      <c r="AC19" s="441"/>
-      <c r="AE19" s="418" t="s">
+      <c r="Q19" s="379"/>
+      <c r="R19" s="379"/>
+      <c r="S19" s="379"/>
+      <c r="T19" s="379"/>
+      <c r="U19" s="379"/>
+      <c r="V19" s="379"/>
+      <c r="W19" s="379"/>
+      <c r="X19" s="379"/>
+      <c r="Y19" s="379"/>
+      <c r="Z19" s="379"/>
+      <c r="AA19" s="379"/>
+      <c r="AB19" s="379"/>
+      <c r="AC19" s="379"/>
+      <c r="AE19" s="380" t="s">
         <v>57</v>
       </c>
-      <c r="AF19" s="420"/>
-      <c r="AG19" s="420"/>
-      <c r="AH19" s="420"/>
-      <c r="AI19" s="420"/>
-      <c r="AJ19" s="420"/>
-      <c r="AK19" s="420"/>
-      <c r="AL19" s="420"/>
-      <c r="AM19" s="420"/>
-      <c r="AN19" s="420"/>
-      <c r="AO19" s="420"/>
-      <c r="AP19" s="420"/>
-      <c r="AQ19" s="420"/>
-      <c r="AR19" s="420"/>
-      <c r="AT19" s="438" t="s">
+      <c r="AF19" s="381"/>
+      <c r="AG19" s="381"/>
+      <c r="AH19" s="381"/>
+      <c r="AI19" s="381"/>
+      <c r="AJ19" s="381"/>
+      <c r="AK19" s="381"/>
+      <c r="AL19" s="381"/>
+      <c r="AM19" s="381"/>
+      <c r="AN19" s="381"/>
+      <c r="AO19" s="381"/>
+      <c r="AP19" s="381"/>
+      <c r="AQ19" s="381"/>
+      <c r="AR19" s="381"/>
+      <c r="AT19" s="378" t="s">
         <v>58</v>
       </c>
-      <c r="AU19" s="438"/>
-      <c r="AV19" s="438"/>
-      <c r="AW19" s="438"/>
-      <c r="AX19" s="438"/>
-      <c r="AY19" s="438"/>
-      <c r="AZ19" s="438"/>
-      <c r="BA19" s="438"/>
-      <c r="BB19" s="438"/>
-      <c r="BC19" s="438"/>
-      <c r="BD19" s="438"/>
-      <c r="BE19" s="438"/>
-      <c r="BF19" s="438"/>
-      <c r="BG19" s="438"/>
-      <c r="BI19" s="416" t="s">
+      <c r="AU19" s="378"/>
+      <c r="AV19" s="378"/>
+      <c r="AW19" s="378"/>
+      <c r="AX19" s="378"/>
+      <c r="AY19" s="378"/>
+      <c r="AZ19" s="378"/>
+      <c r="BA19" s="378"/>
+      <c r="BB19" s="378"/>
+      <c r="BC19" s="378"/>
+      <c r="BD19" s="378"/>
+      <c r="BE19" s="378"/>
+      <c r="BF19" s="378"/>
+      <c r="BG19" s="378"/>
+      <c r="BI19" s="376" t="s">
         <v>59</v>
       </c>
-      <c r="BJ19" s="417"/>
-      <c r="BK19" s="417"/>
-      <c r="BL19" s="417"/>
-      <c r="BM19" s="417"/>
-      <c r="BN19" s="417"/>
-      <c r="BO19" s="417"/>
-      <c r="BP19" s="417"/>
-      <c r="BQ19" s="417"/>
-      <c r="BR19" s="417"/>
-      <c r="BS19" s="417"/>
-      <c r="BT19" s="417"/>
-      <c r="BU19" s="417"/>
-      <c r="BV19" s="417"/>
-      <c r="BX19" s="416" t="s">
+      <c r="BJ19" s="377"/>
+      <c r="BK19" s="377"/>
+      <c r="BL19" s="377"/>
+      <c r="BM19" s="377"/>
+      <c r="BN19" s="377"/>
+      <c r="BO19" s="377"/>
+      <c r="BP19" s="377"/>
+      <c r="BQ19" s="377"/>
+      <c r="BR19" s="377"/>
+      <c r="BS19" s="377"/>
+      <c r="BT19" s="377"/>
+      <c r="BU19" s="377"/>
+      <c r="BV19" s="377"/>
+      <c r="BX19" s="376" t="s">
         <v>60</v>
       </c>
-      <c r="BY19" s="417"/>
-      <c r="BZ19" s="417"/>
-      <c r="CA19" s="417"/>
-      <c r="CB19" s="417"/>
-      <c r="CC19" s="417"/>
-      <c r="CD19" s="417"/>
-      <c r="CE19" s="417"/>
-      <c r="CF19" s="417"/>
-      <c r="CG19" s="417"/>
-      <c r="CH19" s="417"/>
-      <c r="CI19" s="417"/>
-      <c r="CJ19" s="417"/>
-      <c r="CK19" s="417"/>
+      <c r="BY19" s="377"/>
+      <c r="BZ19" s="377"/>
+      <c r="CA19" s="377"/>
+      <c r="CB19" s="377"/>
+      <c r="CC19" s="377"/>
+      <c r="CD19" s="377"/>
+      <c r="CE19" s="377"/>
+      <c r="CF19" s="377"/>
+      <c r="CG19" s="377"/>
+      <c r="CH19" s="377"/>
+      <c r="CI19" s="377"/>
+      <c r="CJ19" s="377"/>
+      <c r="CK19" s="377"/>
       <c r="XDN19" s="1"/>
       <c r="XDO19" s="1"/>
       <c r="XDP19" s="1"/>
@@ -8342,174 +8348,174 @@
       <c r="XFD19" s="1"/>
     </row>
     <row r="20" spans="1:89 16342:16384" s="2" customFormat="1" ht="18" customHeight="1">
-      <c r="A20" s="409" t="s">
+      <c r="A20" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="410"/>
-      <c r="C20" s="409" t="s">
+      <c r="B20" s="375"/>
+      <c r="C20" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="411"/>
-      <c r="E20" s="409" t="s">
+      <c r="D20" s="371"/>
+      <c r="E20" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="412"/>
-      <c r="G20" s="409" t="s">
+      <c r="F20" s="372"/>
+      <c r="G20" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="411"/>
-      <c r="I20" s="409" t="s">
+      <c r="H20" s="371"/>
+      <c r="I20" s="370" t="s">
         <v>11</v>
       </c>
-      <c r="J20" s="411"/>
-      <c r="K20" s="413" t="s">
+      <c r="J20" s="371"/>
+      <c r="K20" s="373" t="s">
         <v>12</v>
       </c>
-      <c r="L20" s="414"/>
-      <c r="M20" s="409" t="s">
+      <c r="L20" s="374"/>
+      <c r="M20" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="N20" s="410"/>
-      <c r="P20" s="409" t="s">
+      <c r="N20" s="375"/>
+      <c r="P20" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="Q20" s="410"/>
-      <c r="R20" s="409" t="s">
+      <c r="Q20" s="375"/>
+      <c r="R20" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="S20" s="411"/>
-      <c r="T20" s="409" t="s">
+      <c r="S20" s="371"/>
+      <c r="T20" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="U20" s="412"/>
-      <c r="V20" s="409" t="s">
+      <c r="U20" s="372"/>
+      <c r="V20" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="W20" s="411"/>
-      <c r="X20" s="409" t="s">
+      <c r="W20" s="371"/>
+      <c r="X20" s="370" t="s">
         <v>11</v>
       </c>
-      <c r="Y20" s="411"/>
-      <c r="Z20" s="413" t="s">
+      <c r="Y20" s="371"/>
+      <c r="Z20" s="373" t="s">
         <v>12</v>
       </c>
-      <c r="AA20" s="414"/>
-      <c r="AB20" s="409" t="s">
+      <c r="AA20" s="374"/>
+      <c r="AB20" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="AC20" s="410"/>
-      <c r="AE20" s="409" t="s">
+      <c r="AC20" s="375"/>
+      <c r="AE20" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="AF20" s="410"/>
-      <c r="AG20" s="409" t="s">
+      <c r="AF20" s="375"/>
+      <c r="AG20" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="AH20" s="411"/>
-      <c r="AI20" s="409" t="s">
+      <c r="AH20" s="371"/>
+      <c r="AI20" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="AJ20" s="412"/>
-      <c r="AK20" s="409" t="s">
+      <c r="AJ20" s="372"/>
+      <c r="AK20" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="AL20" s="411"/>
-      <c r="AM20" s="409" t="s">
+      <c r="AL20" s="371"/>
+      <c r="AM20" s="370" t="s">
         <v>11</v>
       </c>
-      <c r="AN20" s="411"/>
-      <c r="AO20" s="413" t="s">
+      <c r="AN20" s="371"/>
+      <c r="AO20" s="373" t="s">
         <v>12</v>
       </c>
-      <c r="AP20" s="414"/>
-      <c r="AQ20" s="409" t="s">
+      <c r="AP20" s="374"/>
+      <c r="AQ20" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="AR20" s="410"/>
-      <c r="AT20" s="409" t="s">
+      <c r="AR20" s="375"/>
+      <c r="AT20" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="AU20" s="410"/>
-      <c r="AV20" s="409" t="s">
+      <c r="AU20" s="375"/>
+      <c r="AV20" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="AW20" s="409"/>
-      <c r="AX20" s="409" t="s">
+      <c r="AW20" s="370"/>
+      <c r="AX20" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="AY20" s="412"/>
-      <c r="AZ20" s="409" t="s">
+      <c r="AY20" s="372"/>
+      <c r="AZ20" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="BA20" s="411"/>
-      <c r="BB20" s="409" t="s">
+      <c r="BA20" s="371"/>
+      <c r="BB20" s="370" t="s">
         <v>11</v>
       </c>
-      <c r="BC20" s="411"/>
-      <c r="BD20" s="413" t="s">
+      <c r="BC20" s="371"/>
+      <c r="BD20" s="373" t="s">
         <v>12</v>
       </c>
-      <c r="BE20" s="414"/>
-      <c r="BF20" s="409" t="s">
+      <c r="BE20" s="374"/>
+      <c r="BF20" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="BG20" s="410"/>
-      <c r="BI20" s="409" t="s">
+      <c r="BG20" s="375"/>
+      <c r="BI20" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="BJ20" s="410"/>
-      <c r="BK20" s="409" t="s">
+      <c r="BJ20" s="375"/>
+      <c r="BK20" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="BL20" s="411"/>
-      <c r="BM20" s="409" t="s">
+      <c r="BL20" s="371"/>
+      <c r="BM20" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="BN20" s="412"/>
-      <c r="BO20" s="409" t="s">
+      <c r="BN20" s="372"/>
+      <c r="BO20" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="BP20" s="411"/>
-      <c r="BQ20" s="409" t="s">
+      <c r="BP20" s="371"/>
+      <c r="BQ20" s="370" t="s">
         <v>11</v>
       </c>
-      <c r="BR20" s="411"/>
-      <c r="BS20" s="413" t="s">
+      <c r="BR20" s="371"/>
+      <c r="BS20" s="373" t="s">
         <v>12</v>
       </c>
-      <c r="BT20" s="414"/>
-      <c r="BU20" s="409" t="s">
+      <c r="BT20" s="374"/>
+      <c r="BU20" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="BV20" s="410"/>
-      <c r="BX20" s="409" t="s">
+      <c r="BV20" s="375"/>
+      <c r="BX20" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="BY20" s="410"/>
-      <c r="BZ20" s="409" t="s">
+      <c r="BY20" s="375"/>
+      <c r="BZ20" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="CA20" s="411"/>
-      <c r="CB20" s="409" t="s">
+      <c r="CA20" s="371"/>
+      <c r="CB20" s="370" t="s">
         <v>9</v>
       </c>
-      <c r="CC20" s="412"/>
-      <c r="CD20" s="409" t="s">
+      <c r="CC20" s="372"/>
+      <c r="CD20" s="370" t="s">
         <v>10</v>
       </c>
-      <c r="CE20" s="411"/>
-      <c r="CF20" s="409" t="s">
+      <c r="CE20" s="371"/>
+      <c r="CF20" s="370" t="s">
         <v>11</v>
       </c>
-      <c r="CG20" s="411"/>
-      <c r="CH20" s="413" t="s">
+      <c r="CG20" s="371"/>
+      <c r="CH20" s="373" t="s">
         <v>12</v>
       </c>
-      <c r="CI20" s="414"/>
-      <c r="CJ20" s="409" t="s">
+      <c r="CI20" s="374"/>
+      <c r="CJ20" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="CK20" s="410"/>
+      <c r="CK20" s="375"/>
       <c r="XDN20" s="1"/>
       <c r="XDO20" s="1"/>
       <c r="XDP20" s="1"/>
@@ -8555,12 +8561,12 @@
       <c r="XFD20" s="1"/>
     </row>
     <row r="21" spans="1:89 16342:16384" s="2" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A21" s="421"/>
-      <c r="B21" s="425"/>
-      <c r="C21" s="430"/>
-      <c r="D21" s="431"/>
-      <c r="E21" s="421"/>
-      <c r="F21" s="425"/>
+      <c r="A21" s="359"/>
+      <c r="B21" s="360"/>
+      <c r="C21" s="361"/>
+      <c r="D21" s="362"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="360"/>
       <c r="G21" s="5"/>
       <c r="H21" s="6"/>
       <c r="I21" s="5"/>
@@ -9801,22 +9807,22 @@
       <c r="AP25" s="103"/>
       <c r="AQ25" s="5"/>
       <c r="AR25" s="6"/>
-      <c r="AT25" s="442" t="s">
+      <c r="AT25" s="363" t="s">
         <v>14</v>
       </c>
-      <c r="AU25" s="443"/>
-      <c r="AV25" s="443"/>
-      <c r="AW25" s="443"/>
-      <c r="AX25" s="443"/>
-      <c r="AY25" s="443"/>
-      <c r="AZ25" s="443"/>
-      <c r="BA25" s="443"/>
-      <c r="BB25" s="443"/>
-      <c r="BC25" s="443"/>
-      <c r="BD25" s="443"/>
-      <c r="BE25" s="443"/>
-      <c r="BF25" s="443"/>
-      <c r="BG25" s="444"/>
+      <c r="AU25" s="364"/>
+      <c r="AV25" s="364"/>
+      <c r="AW25" s="364"/>
+      <c r="AX25" s="364"/>
+      <c r="AY25" s="364"/>
+      <c r="AZ25" s="364"/>
+      <c r="BA25" s="364"/>
+      <c r="BB25" s="364"/>
+      <c r="BC25" s="364"/>
+      <c r="BD25" s="364"/>
+      <c r="BE25" s="364"/>
+      <c r="BF25" s="364"/>
+      <c r="BG25" s="365"/>
       <c r="BI25" s="248">
         <v>26</v>
       </c>
@@ -9940,64 +9946,64 @@
       <c r="L26" s="251"/>
       <c r="M26" s="15"/>
       <c r="N26" s="254"/>
-      <c r="P26" s="445" t="s">
+      <c r="P26" s="366" t="s">
         <v>19</v>
       </c>
-      <c r="Q26" s="446"/>
-      <c r="R26" s="446"/>
-      <c r="S26" s="446"/>
-      <c r="T26" s="446"/>
-      <c r="U26" s="446"/>
-      <c r="V26" s="446"/>
-      <c r="W26" s="446"/>
-      <c r="X26" s="446"/>
-      <c r="Y26" s="446"/>
-      <c r="Z26" s="446"/>
-      <c r="AA26" s="446"/>
-      <c r="AB26" s="446"/>
-      <c r="AC26" s="446"/>
-      <c r="AD26" s="447"/>
-      <c r="AE26" s="437" t="s">
+      <c r="Q26" s="367"/>
+      <c r="R26" s="367"/>
+      <c r="S26" s="367"/>
+      <c r="T26" s="367"/>
+      <c r="U26" s="367"/>
+      <c r="V26" s="367"/>
+      <c r="W26" s="367"/>
+      <c r="X26" s="367"/>
+      <c r="Y26" s="367"/>
+      <c r="Z26" s="367"/>
+      <c r="AA26" s="367"/>
+      <c r="AB26" s="367"/>
+      <c r="AC26" s="367"/>
+      <c r="AD26" s="368"/>
+      <c r="AE26" s="356" t="s">
         <v>61</v>
       </c>
-      <c r="AF26" s="437"/>
-      <c r="AG26" s="437"/>
-      <c r="AH26" s="437"/>
-      <c r="AI26" s="437"/>
-      <c r="AJ26" s="437"/>
-      <c r="AK26" s="437"/>
-      <c r="AL26" s="437"/>
-      <c r="AM26" s="437"/>
-      <c r="AN26" s="437"/>
-      <c r="AO26" s="437"/>
-      <c r="AP26" s="437"/>
-      <c r="AQ26" s="437"/>
-      <c r="AR26" s="437"/>
-      <c r="AT26" s="448" t="s">
+      <c r="AF26" s="356"/>
+      <c r="AG26" s="356"/>
+      <c r="AH26" s="356"/>
+      <c r="AI26" s="356"/>
+      <c r="AJ26" s="356"/>
+      <c r="AK26" s="356"/>
+      <c r="AL26" s="356"/>
+      <c r="AM26" s="356"/>
+      <c r="AN26" s="356"/>
+      <c r="AO26" s="356"/>
+      <c r="AP26" s="356"/>
+      <c r="AQ26" s="356"/>
+      <c r="AR26" s="356"/>
+      <c r="AT26" s="369" t="s">
         <v>62</v>
       </c>
-      <c r="AU26" s="448"/>
-      <c r="AV26" s="448"/>
-      <c r="AW26" s="448"/>
-      <c r="AX26" s="448"/>
-      <c r="AY26" s="448"/>
-      <c r="AZ26" s="448"/>
-      <c r="BI26" s="450" t="s">
+      <c r="AU26" s="369"/>
+      <c r="AV26" s="369"/>
+      <c r="AW26" s="369"/>
+      <c r="AX26" s="369"/>
+      <c r="AY26" s="369"/>
+      <c r="AZ26" s="369"/>
+      <c r="BI26" s="350" t="s">
         <v>19</v>
       </c>
-      <c r="BJ26" s="451"/>
-      <c r="BK26" s="451"/>
-      <c r="BL26" s="451"/>
-      <c r="BM26" s="451"/>
-      <c r="BN26" s="451"/>
-      <c r="BO26" s="451"/>
-      <c r="BP26" s="451"/>
-      <c r="BQ26" s="451"/>
-      <c r="BR26" s="451"/>
-      <c r="BS26" s="451"/>
-      <c r="BT26" s="451"/>
-      <c r="BU26" s="451"/>
-      <c r="BV26" s="452"/>
+      <c r="BJ26" s="351"/>
+      <c r="BK26" s="351"/>
+      <c r="BL26" s="351"/>
+      <c r="BM26" s="351"/>
+      <c r="BN26" s="351"/>
+      <c r="BO26" s="351"/>
+      <c r="BP26" s="351"/>
+      <c r="BQ26" s="351"/>
+      <c r="BR26" s="351"/>
+      <c r="BS26" s="351"/>
+      <c r="BT26" s="351"/>
+      <c r="BU26" s="351"/>
+      <c r="BV26" s="352"/>
       <c r="BX26" s="15"/>
       <c r="BY26" s="251"/>
       <c r="BZ26" s="15"/>
@@ -10057,32 +10063,32 @@
       <c r="XFD26" s="1"/>
     </row>
     <row r="27" spans="1:89 16342:16384" s="2" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="A27" s="453" t="s">
+      <c r="A27" s="353" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="453"/>
-      <c r="C27" s="453"/>
-      <c r="D27" s="453"/>
-      <c r="E27" s="453"/>
-      <c r="F27" s="453"/>
-      <c r="G27" s="453"/>
-      <c r="H27" s="453"/>
-      <c r="I27" s="453"/>
-      <c r="J27" s="453"/>
-      <c r="K27" s="453"/>
-      <c r="L27" s="453"/>
-      <c r="M27" s="453"/>
-      <c r="N27" s="453"/>
-      <c r="AE27" s="433" t="s">
+      <c r="B27" s="353"/>
+      <c r="C27" s="353"/>
+      <c r="D27" s="353"/>
+      <c r="E27" s="353"/>
+      <c r="F27" s="353"/>
+      <c r="G27" s="353"/>
+      <c r="H27" s="353"/>
+      <c r="I27" s="353"/>
+      <c r="J27" s="353"/>
+      <c r="K27" s="353"/>
+      <c r="L27" s="353"/>
+      <c r="M27" s="353"/>
+      <c r="N27" s="353"/>
+      <c r="AE27" s="354" t="s">
         <v>63</v>
       </c>
-      <c r="AF27" s="433"/>
-      <c r="AG27" s="433"/>
-      <c r="AH27" s="433"/>
-      <c r="AI27" s="433"/>
-      <c r="AJ27" s="433"/>
-      <c r="AK27" s="433"/>
-      <c r="AL27" s="433"/>
+      <c r="AF27" s="354"/>
+      <c r="AG27" s="354"/>
+      <c r="AH27" s="354"/>
+      <c r="AI27" s="354"/>
+      <c r="AJ27" s="354"/>
+      <c r="AK27" s="354"/>
+      <c r="AL27" s="354"/>
       <c r="AM27" s="129"/>
       <c r="AN27" s="256"/>
       <c r="AO27" s="256"/>
@@ -10096,30 +10102,30 @@
         <v>65</v>
       </c>
       <c r="AV27" s="3"/>
-      <c r="BI27" s="454" t="s">
+      <c r="BI27" s="355" t="s">
         <v>66</v>
       </c>
-      <c r="BJ27" s="454"/>
-      <c r="BK27" s="454"/>
-      <c r="BL27" s="454"/>
-      <c r="BM27" s="454"/>
-      <c r="BN27" s="454"/>
-      <c r="BX27" s="437" t="s">
+      <c r="BJ27" s="355"/>
+      <c r="BK27" s="355"/>
+      <c r="BL27" s="355"/>
+      <c r="BM27" s="355"/>
+      <c r="BN27" s="355"/>
+      <c r="BX27" s="356" t="s">
         <v>61</v>
       </c>
-      <c r="BY27" s="437"/>
-      <c r="BZ27" s="437"/>
-      <c r="CA27" s="437"/>
-      <c r="CB27" s="437"/>
-      <c r="CC27" s="437"/>
-      <c r="CD27" s="437"/>
-      <c r="CE27" s="437"/>
-      <c r="CF27" s="437"/>
-      <c r="CG27" s="437"/>
-      <c r="CH27" s="437"/>
-      <c r="CI27" s="437"/>
-      <c r="CJ27" s="437"/>
-      <c r="CK27" s="437"/>
+      <c r="BY27" s="356"/>
+      <c r="BZ27" s="356"/>
+      <c r="CA27" s="356"/>
+      <c r="CB27" s="356"/>
+      <c r="CC27" s="356"/>
+      <c r="CD27" s="356"/>
+      <c r="CE27" s="356"/>
+      <c r="CF27" s="356"/>
+      <c r="CG27" s="356"/>
+      <c r="CH27" s="356"/>
+      <c r="CI27" s="356"/>
+      <c r="CJ27" s="356"/>
+      <c r="CK27" s="356"/>
       <c r="XDN27" s="1"/>
       <c r="XDO27" s="1"/>
       <c r="XDP27" s="1"/>
@@ -10165,31 +10171,31 @@
       <c r="XFD27" s="1"/>
     </row>
     <row r="28" spans="1:89 16342:16384" s="2" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A28" s="433" t="s">
+      <c r="A28" s="354" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="433"/>
-      <c r="C28" s="433"/>
-      <c r="D28" s="433"/>
-      <c r="E28" s="433"/>
-      <c r="F28" s="433"/>
-      <c r="G28" s="433"/>
-      <c r="P28" s="433" t="s">
+      <c r="B28" s="354"/>
+      <c r="C28" s="354"/>
+      <c r="D28" s="354"/>
+      <c r="E28" s="354"/>
+      <c r="F28" s="354"/>
+      <c r="G28" s="354"/>
+      <c r="P28" s="354" t="s">
         <v>68</v>
       </c>
-      <c r="Q28" s="433"/>
-      <c r="R28" s="433"/>
-      <c r="S28" s="433"/>
-      <c r="T28" s="433"/>
-      <c r="U28" s="433"/>
-      <c r="V28" s="433"/>
+      <c r="Q28" s="354"/>
+      <c r="R28" s="354"/>
+      <c r="S28" s="354"/>
+      <c r="T28" s="354"/>
+      <c r="U28" s="354"/>
+      <c r="V28" s="354"/>
       <c r="W28" s="128"/>
       <c r="X28" s="128"/>
-      <c r="Y28" s="455"/>
-      <c r="Z28" s="455"/>
-      <c r="AA28" s="455"/>
-      <c r="AB28" s="455"/>
-      <c r="AC28" s="455"/>
+      <c r="Y28" s="357"/>
+      <c r="Z28" s="357"/>
+      <c r="AA28" s="357"/>
+      <c r="AB28" s="357"/>
+      <c r="AC28" s="357"/>
       <c r="AE28" s="21">
         <v>6</v>
       </c>
@@ -10215,15 +10221,15 @@
       <c r="BJ28" s="152" t="s">
         <v>31</v>
       </c>
-      <c r="BX28" s="456" t="s">
+      <c r="BX28" s="358" t="s">
         <v>71</v>
       </c>
-      <c r="BY28" s="456"/>
-      <c r="BZ28" s="456"/>
-      <c r="CA28" s="456"/>
-      <c r="CB28" s="456"/>
-      <c r="CC28" s="456"/>
-      <c r="CD28" s="456"/>
+      <c r="BY28" s="358"/>
+      <c r="BZ28" s="358"/>
+      <c r="CA28" s="358"/>
+      <c r="CB28" s="358"/>
+      <c r="CC28" s="358"/>
+      <c r="CD28" s="358"/>
       <c r="XDN28" s="1"/>
       <c r="XDO28" s="1"/>
       <c r="XDP28" s="1"/>
@@ -10585,13 +10591,13 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="129"/>
-      <c r="H32" s="449"/>
-      <c r="I32" s="449"/>
-      <c r="J32" s="449"/>
-      <c r="K32" s="449"/>
-      <c r="L32" s="449"/>
-      <c r="M32" s="449"/>
-      <c r="N32" s="449"/>
+      <c r="H32" s="349"/>
+      <c r="I32" s="349"/>
+      <c r="J32" s="349"/>
+      <c r="K32" s="349"/>
+      <c r="L32" s="349"/>
+      <c r="M32" s="349"/>
+      <c r="N32" s="349"/>
       <c r="P32" s="21">
         <v>4</v>
       </c>
@@ -12943,16 +12949,125 @@
     <row r="87" spans="1:44" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="153">
-    <mergeCell ref="H32:N32"/>
-    <mergeCell ref="BI26:BV26"/>
-    <mergeCell ref="A27:N27"/>
-    <mergeCell ref="AE27:AL27"/>
-    <mergeCell ref="BI27:BN27"/>
-    <mergeCell ref="BX27:CK27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="Y28:AC28"/>
-    <mergeCell ref="BX28:CD28"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A1:CK1"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="P3:AC3"/>
+    <mergeCell ref="AE3:AR3"/>
+    <mergeCell ref="AT3:BG3"/>
+    <mergeCell ref="BI3:BV3"/>
+    <mergeCell ref="BX3:CK3"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="AI4:AJ4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="AZ4:BA4"/>
+    <mergeCell ref="BB4:BC4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="BF4:BG4"/>
+    <mergeCell ref="BI4:BJ4"/>
+    <mergeCell ref="BK4:BL4"/>
+    <mergeCell ref="AM4:AN4"/>
+    <mergeCell ref="AO4:AP4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="AT4:AU4"/>
+    <mergeCell ref="AV4:AW4"/>
+    <mergeCell ref="AX4:AY4"/>
+    <mergeCell ref="BZ4:CA4"/>
+    <mergeCell ref="CB4:CC4"/>
+    <mergeCell ref="CD4:CE4"/>
+    <mergeCell ref="CF4:CG4"/>
+    <mergeCell ref="CH4:CI4"/>
+    <mergeCell ref="CJ4:CK4"/>
+    <mergeCell ref="BM4:BN4"/>
+    <mergeCell ref="BO4:BP4"/>
+    <mergeCell ref="BQ4:BR4"/>
+    <mergeCell ref="BS4:BT4"/>
+    <mergeCell ref="BU4:BV4"/>
+    <mergeCell ref="BX4:BY4"/>
+    <mergeCell ref="AO5:AP5"/>
+    <mergeCell ref="AT5:AU5"/>
+    <mergeCell ref="AV5:AW5"/>
+    <mergeCell ref="AX5:AY5"/>
+    <mergeCell ref="AZ5:BA5"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="AG5:AH5"/>
+    <mergeCell ref="AI5:AJ5"/>
+    <mergeCell ref="AK5:AL5"/>
+    <mergeCell ref="AM5:AN5"/>
+    <mergeCell ref="BB10:BC10"/>
+    <mergeCell ref="BD10:BE10"/>
+    <mergeCell ref="BF10:BG10"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="P11:W11"/>
+    <mergeCell ref="AE11:AR11"/>
+    <mergeCell ref="AT11:BG11"/>
+    <mergeCell ref="AO10:AP10"/>
+    <mergeCell ref="AQ10:AR10"/>
+    <mergeCell ref="AT10:AU10"/>
+    <mergeCell ref="AV10:AW10"/>
+    <mergeCell ref="AX10:AY10"/>
+    <mergeCell ref="AZ10:BA10"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="P10:AC10"/>
+    <mergeCell ref="AG10:AH10"/>
+    <mergeCell ref="AI10:AJ10"/>
+    <mergeCell ref="AK10:AL10"/>
+    <mergeCell ref="AM10:AN10"/>
+    <mergeCell ref="AT19:BG19"/>
+    <mergeCell ref="BI19:BV19"/>
+    <mergeCell ref="BX19:CK19"/>
+    <mergeCell ref="BI11:BV11"/>
+    <mergeCell ref="BX11:CK11"/>
+    <mergeCell ref="AE12:AM12"/>
+    <mergeCell ref="AT12:AZ12"/>
+    <mergeCell ref="BA12:BG12"/>
+    <mergeCell ref="BI12:BN12"/>
+    <mergeCell ref="BX12:CC12"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="A19:N19"/>
+    <mergeCell ref="P19:AC19"/>
+    <mergeCell ref="AE19:AR19"/>
+    <mergeCell ref="AG20:AH20"/>
+    <mergeCell ref="AI20:AJ20"/>
+    <mergeCell ref="AK20:AL20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="CD20:CE20"/>
+    <mergeCell ref="CF20:CG20"/>
+    <mergeCell ref="CH20:CI20"/>
+    <mergeCell ref="CJ20:CK20"/>
+    <mergeCell ref="BM20:BN20"/>
+    <mergeCell ref="BO20:BP20"/>
+    <mergeCell ref="BQ20:BR20"/>
+    <mergeCell ref="BS20:BT20"/>
+    <mergeCell ref="BU20:BV20"/>
+    <mergeCell ref="BX20:BY20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="E21:F21"/>
@@ -12977,125 +13092,16 @@
     <mergeCell ref="Z20:AA20"/>
     <mergeCell ref="AB20:AC20"/>
     <mergeCell ref="AE20:AF20"/>
-    <mergeCell ref="CD20:CE20"/>
-    <mergeCell ref="CF20:CG20"/>
-    <mergeCell ref="CH20:CI20"/>
-    <mergeCell ref="CJ20:CK20"/>
-    <mergeCell ref="BM20:BN20"/>
-    <mergeCell ref="BO20:BP20"/>
-    <mergeCell ref="BQ20:BR20"/>
-    <mergeCell ref="BS20:BT20"/>
-    <mergeCell ref="BU20:BV20"/>
-    <mergeCell ref="BX20:BY20"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="A19:N19"/>
-    <mergeCell ref="P19:AC19"/>
-    <mergeCell ref="AE19:AR19"/>
-    <mergeCell ref="AG20:AH20"/>
-    <mergeCell ref="AI20:AJ20"/>
-    <mergeCell ref="AK20:AL20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="AT19:BG19"/>
-    <mergeCell ref="BI19:BV19"/>
-    <mergeCell ref="BX19:CK19"/>
-    <mergeCell ref="BI11:BV11"/>
-    <mergeCell ref="BX11:CK11"/>
-    <mergeCell ref="AE12:AM12"/>
-    <mergeCell ref="AT12:AZ12"/>
-    <mergeCell ref="BA12:BG12"/>
-    <mergeCell ref="BI12:BN12"/>
-    <mergeCell ref="BX12:CC12"/>
-    <mergeCell ref="BB10:BC10"/>
-    <mergeCell ref="BD10:BE10"/>
-    <mergeCell ref="BF10:BG10"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="P11:W11"/>
-    <mergeCell ref="AE11:AR11"/>
-    <mergeCell ref="AT11:BG11"/>
-    <mergeCell ref="AO10:AP10"/>
-    <mergeCell ref="AQ10:AR10"/>
-    <mergeCell ref="AT10:AU10"/>
-    <mergeCell ref="AV10:AW10"/>
-    <mergeCell ref="AX10:AY10"/>
-    <mergeCell ref="AZ10:BA10"/>
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="P10:AC10"/>
-    <mergeCell ref="AG10:AH10"/>
-    <mergeCell ref="AI10:AJ10"/>
-    <mergeCell ref="AK10:AL10"/>
-    <mergeCell ref="AM10:AN10"/>
-    <mergeCell ref="AO5:AP5"/>
-    <mergeCell ref="AT5:AU5"/>
-    <mergeCell ref="AV5:AW5"/>
-    <mergeCell ref="AX5:AY5"/>
-    <mergeCell ref="AZ5:BA5"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="AE5:AF5"/>
-    <mergeCell ref="AG5:AH5"/>
-    <mergeCell ref="AI5:AJ5"/>
-    <mergeCell ref="AK5:AL5"/>
-    <mergeCell ref="AM5:AN5"/>
-    <mergeCell ref="BZ4:CA4"/>
-    <mergeCell ref="CB4:CC4"/>
-    <mergeCell ref="CD4:CE4"/>
-    <mergeCell ref="CF4:CG4"/>
-    <mergeCell ref="CH4:CI4"/>
-    <mergeCell ref="CJ4:CK4"/>
-    <mergeCell ref="BM4:BN4"/>
-    <mergeCell ref="BO4:BP4"/>
-    <mergeCell ref="BQ4:BR4"/>
-    <mergeCell ref="BS4:BT4"/>
-    <mergeCell ref="BU4:BV4"/>
-    <mergeCell ref="BX4:BY4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="AZ4:BA4"/>
-    <mergeCell ref="BB4:BC4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="BF4:BG4"/>
-    <mergeCell ref="BI4:BJ4"/>
-    <mergeCell ref="BK4:BL4"/>
-    <mergeCell ref="AM4:AN4"/>
-    <mergeCell ref="AO4:AP4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="AT4:AU4"/>
-    <mergeCell ref="AV4:AW4"/>
-    <mergeCell ref="AX4:AY4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A1:CK1"/>
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="P3:AC3"/>
-    <mergeCell ref="AE3:AR3"/>
-    <mergeCell ref="AT3:BG3"/>
-    <mergeCell ref="BI3:BV3"/>
-    <mergeCell ref="BX3:CK3"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="AI4:AJ4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="H32:N32"/>
+    <mergeCell ref="BI26:BV26"/>
+    <mergeCell ref="A27:N27"/>
+    <mergeCell ref="AE27:AL27"/>
+    <mergeCell ref="BI27:BN27"/>
+    <mergeCell ref="BX27:CK27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="Y28:AC28"/>
+    <mergeCell ref="BX28:CD28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
